--- a/database/event/6018/event_6018_evp_summary.xlsx
+++ b/database/event/6018/event_6018_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.34</v>
+        <v>8.331899999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1793</v>
+        <v>1.1782</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9478</v>
+        <v>2.8755</v>
       </c>
       <c r="E2" t="n">
-        <v>8.34</v>
+        <v>8.331899999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1519</v>
+        <v>2.1439</v>
       </c>
       <c r="G2" t="n">
         <v>6.188</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1519</v>
+        <v>2.1439</v>
       </c>
       <c r="I2" t="n">
         <v>2.1619</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7763</v>
+        <v>7.7702</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0996</v>
+        <v>1.0988</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7201</v>
+        <v>2.6517</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7763</v>
+        <v>7.7702</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6242</v>
+        <v>1.6181</v>
       </c>
       <c r="G3" t="n">
         <v>6.1521</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6242</v>
+        <v>1.6181</v>
       </c>
       <c r="I3" t="n">
         <v>1.6317</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.1237</v>
+        <v>6.6888</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8659</v>
+        <v>0.9459</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0525</v>
+        <v>2.2209</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1237</v>
+        <v>6.6888</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3659</v>
+        <v>2.931</v>
       </c>
       <c r="G4" t="n">
         <v>3.7578</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3659</v>
+        <v>2.931</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9176</v>
+        <v>2.3757</v>
       </c>
       <c r="J4" t="n">
         <v>3.7578</v>
@@ -621,7 +621,7 @@
         <v>175</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6754</v>
+        <v>6.1335</v>
       </c>
       <c r="N4" t="n">
         <v>268</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.716</v>
+        <v>5.7169</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8083</v>
+        <v>0.8084</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8878</v>
+        <v>1.8337</v>
       </c>
       <c r="E5" t="n">
-        <v>5.716</v>
+        <v>5.7169</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2243</v>
+        <v>-0.2234</v>
       </c>
       <c r="G5" t="n">
         <v>5.9403</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2243</v>
+        <v>-0.2234</v>
       </c>
       <c r="I5" t="n">
         <v>-0.2253</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.3082</v>
+        <v>3.8733</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4678</v>
+        <v>0.5477</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9151</v>
+        <v>1.0992</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3082</v>
+        <v>3.8733</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9568</v>
+        <v>3.5219</v>
       </c>
       <c r="G6" t="n">
         <v>0.3514</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9568</v>
+        <v>3.5219</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3965</v>
+        <v>2.8546</v>
       </c>
       <c r="J6" t="n">
         <v>0.3514</v>
@@ -713,7 +713,7 @@
         <v>175</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7479</v>
+        <v>3.206</v>
       </c>
       <c r="N6" t="n">
         <v>268</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1456</v>
+        <v>3.6312</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4448</v>
+        <v>0.5135</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8494</v>
+        <v>1.0028</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1456</v>
+        <v>3.6312</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4948</v>
+        <v>1.9804</v>
       </c>
       <c r="G7" t="n">
         <v>1.6508</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4948</v>
+        <v>1.9804</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4948</v>
+        <v>1.9804</v>
       </c>
       <c r="J7" t="n">
         <v>1.6508</v>
@@ -759,7 +759,7 @@
         <v>106</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1456</v>
+        <v>3.6312</v>
       </c>
       <c r="N7" t="n">
         <v>194</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7522</v>
+        <v>2.7436</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3892</v>
+        <v>0.388</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6905</v>
+        <v>0.6491</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7522</v>
+        <v>2.7436</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3184</v>
+        <v>2.3098</v>
       </c>
       <c r="G8" t="n">
         <v>0.4338</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3184</v>
+        <v>2.3098</v>
       </c>
       <c r="I8" t="n">
         <v>2.3292</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7042</v>
+        <v>2.7073</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3824</v>
+        <v>0.3828</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6711</v>
+        <v>0.6347</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7042</v>
+        <v>2.7073</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>3.5243</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="I9" t="n">
         <v>-0.8239</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6675</v>
+        <v>2.662</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3772</v>
+        <v>0.3764</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6562</v>
+        <v>0.6166</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6675</v>
+        <v>2.662</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4793</v>
+        <v>1.4738</v>
       </c>
       <c r="G10" t="n">
         <v>1.1882</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4793</v>
+        <v>1.4738</v>
       </c>
       <c r="I10" t="n">
         <v>1.4862</v>
@@ -916,7 +916,7 @@
         <v>0.3624</v>
       </c>
       <c r="D11" t="n">
-        <v>0.614</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>2.5629</v>
@@ -962,7 +962,7 @@
         <v>0.3492</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5762</v>
+        <v>0.5399</v>
       </c>
       <c r="E12" t="n">
         <v>2.4694</v>
@@ -1008,7 +1008,7 @@
         <v>0.3468</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5695</v>
+        <v>0.5333</v>
       </c>
       <c r="E13" t="n">
         <v>2.4528</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5201</v>
+        <v>1.8965</v>
       </c>
       <c r="C14" t="n">
-        <v>0.215</v>
+        <v>0.2682</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1927</v>
+        <v>0.3117</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5201</v>
+        <v>1.8965</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8679</v>
+        <v>2.2443</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3478</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8679</v>
+        <v>2.2443</v>
       </c>
       <c r="I14" t="n">
-        <v>1.514</v>
+        <v>1.8191</v>
       </c>
       <c r="J14" t="n">
         <v>-0.3478</v>
@@ -1081,7 +1081,7 @@
         <v>49</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1662</v>
+        <v>1.4713</v>
       </c>
       <c r="N14" t="n">
         <v>138</v>
@@ -1090,81 +1090,81 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DeathZz</t>
+          <t>REDSTAR</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1038</v>
+        <v>1.1336</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1561</v>
+        <v>0.1603</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0245</v>
+        <v>0.0077</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1038</v>
+        <v>1.1336</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7255</v>
+        <v>1.3164</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6217</v>
+        <v>-0.1828</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7255</v>
+        <v>1.3164</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7335</v>
+        <v>1.3164</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6217</v>
+        <v>-0.1828</v>
       </c>
       <c r="K15" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1118</v>
+        <v>1.1336</v>
       </c>
       <c r="N15" t="n">
-        <v>133</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mopoz</t>
+          <t>DeathZz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9991</v>
+        <v>1.0973</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1413</v>
+        <v>0.1552</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0177</v>
+        <v>-0.0067</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9991</v>
+        <v>1.0973</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6853</v>
+        <v>1.719</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3138</v>
+        <v>-0.6217</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6853</v>
+        <v>1.719</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6885</v>
+        <v>1.7335</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3138</v>
+        <v>-0.6217</v>
       </c>
       <c r="K16" t="n">
         <v>76</v>
@@ -1173,7 +1173,7 @@
         <v>57</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0023</v>
+        <v>1.1118</v>
       </c>
       <c r="N16" t="n">
         <v>133</v>
@@ -1182,127 +1182,127 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REDSTAR</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8874</v>
+        <v>0.9973</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1255</v>
+        <v>0.141</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0629</v>
+        <v>-0.0466</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8874</v>
+        <v>0.9973</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0702</v>
+        <v>0.3956</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1828</v>
+        <v>0.6017</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0702</v>
+        <v>0.3956</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0702</v>
+        <v>0.3989</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1828</v>
+        <v>0.6017</v>
       </c>
       <c r="K17" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="L17" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8874000000000001</v>
+        <v>1.0006</v>
       </c>
       <c r="N17" t="n">
-        <v>194</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>forsyy</t>
+          <t>mopoz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8286</v>
+        <v>0.9966</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1172</v>
+        <v>0.1409</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0866</v>
+        <v>-0.0469</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8286</v>
+        <v>0.9966</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4706</v>
+        <v>0.6828</v>
       </c>
       <c r="G18" t="n">
-        <v>0.358</v>
+        <v>0.3138</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4706</v>
+        <v>0.6828</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4728</v>
+        <v>0.6885</v>
       </c>
       <c r="J18" t="n">
-        <v>0.358</v>
+        <v>0.3138</v>
       </c>
       <c r="K18" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="L18" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8308</v>
+        <v>1.0023</v>
       </c>
       <c r="N18" t="n">
-        <v>171</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>forsyy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8</v>
+        <v>0.8269</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1131</v>
+        <v>0.1169</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0982</v>
+        <v>-0.1145</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8</v>
+        <v>0.8269</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1983</v>
+        <v>0.4689</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6017</v>
+        <v>0.358</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1983</v>
+        <v>0.4689</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1992</v>
+        <v>0.4728</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6017</v>
+        <v>0.358</v>
       </c>
       <c r="K19" t="n">
         <v>102</v>
@@ -1311,7 +1311,7 @@
         <v>69</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8308</v>
       </c>
       <c r="N19" t="n">
         <v>171</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SHiPZ</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5603</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0843</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.195</v>
+        <v>-0.2063</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5603</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.199</v>
+        <v>1.4365</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3613</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.199</v>
+        <v>1.4365</v>
       </c>
       <c r="I20" t="n">
-        <v>0.199</v>
+        <v>1.1643</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3613</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L20" t="n">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5603</v>
+        <v>0.3240999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>194</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>SHiPZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3672</v>
+        <v>0.5603</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0519</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.273</v>
+        <v>-0.2207</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3672</v>
+        <v>0.5603</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2074</v>
+        <v>0.199</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8401999999999999</v>
+        <v>0.3613</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2074</v>
+        <v>0.199</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9786</v>
+        <v>0.199</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8401999999999999</v>
+        <v>0.3613</v>
       </c>
       <c r="K21" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L21" t="n">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1384000000000001</v>
+        <v>0.5603</v>
       </c>
       <c r="N21" t="n">
-        <v>138</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22">
@@ -1422,7 +1422,7 @@
         <v>0.0348</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3218</v>
+        <v>-0.3457</v>
       </c>
       <c r="E22" t="n">
         <v>0.2464</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1364</v>
+        <v>0.1342</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0193</v>
+        <v>0.019</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3663</v>
+        <v>-0.3904</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1364</v>
+        <v>0.1342</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6129</v>
+        <v>0.6107</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4765</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6129</v>
+        <v>0.6107</v>
       </c>
       <c r="I23" t="n">
         <v>0.6158</v>
@@ -1514,7 +1514,7 @@
         <v>0.0004</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4202</v>
+        <v>-0.4428</v>
       </c>
       <c r="E24" t="n">
         <v>0.0029</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0276</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5001</v>
+        <v>-0.5216</v>
       </c>
       <c r="E25" t="n">
         <v>-0.1949</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0351</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5216</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="E26" t="n">
         <v>-0.2482</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0369</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.5478</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2608</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0549</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5782</v>
+        <v>-0.5986</v>
       </c>
       <c r="E28" t="n">
         <v>-0.3882</v>
@@ -1744,7 +1744,7 @@
         <v>-0.082</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.675</v>
       </c>
       <c r="E29" t="n">
         <v>-0.58</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6442</v>
+        <v>-0.6127</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0911</v>
+        <v>-0.0866</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6816</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6442</v>
+        <v>-0.6127</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0457</v>
+        <v>0.0772</v>
       </c>
       <c r="G30" t="n">
         <v>-0.6899</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0457</v>
+        <v>0.0772</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0459</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>-0.6899</v>
@@ -1817,7 +1817,7 @@
         <v>69</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6439999999999999</v>
+        <v>-0.6121</v>
       </c>
       <c r="N30" t="n">
         <v>171</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>ADEJIS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6565</v>
+        <v>-0.6319</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6866</v>
+        <v>-0.6957</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6565</v>
+        <v>-0.6319</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4988</v>
+        <v>0.3681</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1577</v>
+        <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4988</v>
+        <v>0.3681</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4043</v>
+        <v>0.3712</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1577</v>
+        <v>-1</v>
       </c>
       <c r="K31" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="L31" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.6288</v>
       </c>
       <c r="N31" t="n">
-        <v>138</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ADEJIS</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7547</v>
+        <v>-0.6565</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1067</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7262</v>
+        <v>-0.7055</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7547</v>
+        <v>-0.6565</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2453</v>
+        <v>-0.4988</v>
       </c>
       <c r="G32" t="n">
-        <v>-1</v>
+        <v>-0.1577</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2453</v>
+        <v>-0.4988</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2465</v>
+        <v>-0.4043</v>
       </c>
       <c r="J32" t="n">
-        <v>-1</v>
+        <v>-0.1577</v>
       </c>
       <c r="K32" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="L32" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7535000000000001</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>171</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33">
@@ -1928,7 +1928,7 @@
         <v>-0.1233</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7736</v>
+        <v>-0.7913</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8719</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1365</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8114</v>
+        <v>-0.8286</v>
       </c>
       <c r="E34" t="n">
         <v>-0.9655</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1486</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8459</v>
+        <v>-0.8625</v>
       </c>
       <c r="E35" t="n">
         <v>-1.0508</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1569</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.8859</v>
       </c>
       <c r="E36" t="n">
         <v>-1.1094</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2129</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0295</v>
+        <v>-1.0437</v>
       </c>
       <c r="E37" t="n">
         <v>-1.5054</v>
@@ -2158,7 +2158,7 @@
         <v>-0.2518</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1408</v>
+        <v>-1.1535</v>
       </c>
       <c r="E38" t="n">
         <v>-1.781</v>
@@ -2204,7 +2204,7 @@
         <v>-0.2649</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1782</v>
+        <v>-1.1903</v>
       </c>
       <c r="E39" t="n">
         <v>-1.8735</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0931</v>
+        <v>-2.0862</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.296</v>
+        <v>-0.295</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2669</v>
+        <v>-1.2751</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0931</v>
+        <v>-2.0862</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8616</v>
+        <v>-1.8547</v>
       </c>
       <c r="G40" t="n">
         <v>-0.2315</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8616</v>
+        <v>-1.8547</v>
       </c>
       <c r="I40" t="n">
         <v>-1.8703</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.5679</v>
+        <v>-2.5618</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3631</v>
+        <v>-0.3623</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4587</v>
+        <v>-1.4645</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.5679</v>
+        <v>-2.5618</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6377</v>
+        <v>-1.6316</v>
       </c>
       <c r="G41" t="n">
         <v>-0.9302</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6377</v>
+        <v>-1.6316</v>
       </c>
       <c r="I41" t="n">
         <v>-1.6453</v>

--- a/database/event/6018/event_6018_evp_summary.xlsx
+++ b/database/event/6018/event_6018_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.331899999999999</v>
+        <v>8.494300000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1782</v>
+        <v>1.2012</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8755</v>
+        <v>3.1967</v>
       </c>
       <c r="E2" t="n">
-        <v>8.331899999999999</v>
+        <v>8.494300000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1439</v>
+        <v>3.0062</v>
       </c>
       <c r="G2" t="n">
-        <v>6.188</v>
+        <v>5.4881</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1439</v>
+        <v>3.2413</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1619</v>
+        <v>3.3746</v>
       </c>
       <c r="J2" t="n">
-        <v>6.188</v>
+        <v>5.4881</v>
       </c>
       <c r="K2" t="n">
         <v>79</v>
@@ -529,7 +529,7 @@
         <v>244</v>
       </c>
       <c r="M2" t="n">
-        <v>8.3499</v>
+        <v>8.8627</v>
       </c>
       <c r="N2" t="n">
         <v>323</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7702</v>
+        <v>7.0726</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0988</v>
+        <v>1.0001</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6517</v>
+        <v>2.5549</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7702</v>
+        <v>7.0726</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6181</v>
+        <v>1.5806</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1521</v>
+        <v>5.492</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6181</v>
+        <v>1.5806</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6317</v>
+        <v>1.6456</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1521</v>
+        <v>5.492</v>
       </c>
       <c r="K3" t="n">
         <v>79</v>
@@ -575,7 +575,7 @@
         <v>244</v>
       </c>
       <c r="M3" t="n">
-        <v>7.783799999999999</v>
+        <v>7.1376</v>
       </c>
       <c r="N3" t="n">
         <v>323</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.6888</v>
+        <v>6.2445</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9459</v>
+        <v>0.883</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2209</v>
+        <v>2.1811</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6888</v>
+        <v>6.2445</v>
       </c>
       <c r="F4" t="n">
-        <v>2.931</v>
+        <v>2.8776</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7578</v>
+        <v>3.3669</v>
       </c>
       <c r="H4" t="n">
-        <v>2.931</v>
+        <v>4.6524</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3757</v>
+        <v>2.4191</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7578</v>
+        <v>3.3669</v>
       </c>
       <c r="K4" t="n">
         <v>93</v>
@@ -621,7 +621,7 @@
         <v>175</v>
       </c>
       <c r="M4" t="n">
-        <v>6.1335</v>
+        <v>5.786</v>
       </c>
       <c r="N4" t="n">
         <v>268</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7169</v>
+        <v>5.3235</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8084</v>
+        <v>0.7528</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8337</v>
+        <v>1.7653</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7169</v>
+        <v>5.3235</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2234</v>
+        <v>0.0016</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9403</v>
+        <v>5.3219</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2234</v>
+        <v>0.0016</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2253</v>
+        <v>0.0017</v>
       </c>
       <c r="J5" t="n">
-        <v>5.9403</v>
+        <v>5.3219</v>
       </c>
       <c r="K5" t="n">
         <v>79</v>
@@ -667,7 +667,7 @@
         <v>244</v>
       </c>
       <c r="M5" t="n">
-        <v>5.715</v>
+        <v>5.3236</v>
       </c>
       <c r="N5" t="n">
         <v>323</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8733</v>
+        <v>3.5999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5477</v>
+        <v>0.5091</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0992</v>
+        <v>0.9872</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8733</v>
+        <v>3.5999</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5219</v>
+        <v>3.0796</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3514</v>
+        <v>0.5203</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5219</v>
+        <v>5.3644</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8546</v>
+        <v>2.7892</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3514</v>
+        <v>0.5203</v>
       </c>
       <c r="K6" t="n">
         <v>93</v>
@@ -713,7 +713,7 @@
         <v>175</v>
       </c>
       <c r="M6" t="n">
-        <v>3.206</v>
+        <v>3.3095</v>
       </c>
       <c r="N6" t="n">
         <v>268</v>
@@ -722,173 +722,173 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>h4rn</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6312</v>
+        <v>3.4446</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5135</v>
+        <v>0.4871</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0028</v>
+        <v>0.9171</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6312</v>
+        <v>3.4446</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9804</v>
+        <v>2.3095</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6508</v>
+        <v>1.1351</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9804</v>
+        <v>2.3095</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9804</v>
+        <v>2.4045</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6508</v>
+        <v>1.1351</v>
       </c>
       <c r="K7" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="L7" t="n">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6312</v>
+        <v>3.5396</v>
       </c>
       <c r="N7" t="n">
-        <v>194</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>Forester</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7436</v>
+        <v>3.302</v>
       </c>
       <c r="C8" t="n">
-        <v>0.388</v>
+        <v>0.4669</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6491</v>
+        <v>0.8527</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7436</v>
+        <v>3.302</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3098</v>
+        <v>2.8906</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4338</v>
+        <v>0.4114</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3098</v>
+        <v>4.6983</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3292</v>
+        <v>2.4429</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4338</v>
+        <v>0.4114</v>
       </c>
       <c r="K8" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="L8" t="n">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="M8" t="n">
-        <v>2.763</v>
+        <v>2.8543</v>
       </c>
       <c r="N8" t="n">
-        <v>133</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>h4rn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7073</v>
+        <v>3.2813</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3828</v>
+        <v>0.464</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6347</v>
+        <v>0.8433</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7073</v>
+        <v>3.2813</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8169999999999999</v>
+        <v>1.9663</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5243</v>
+        <v>1.315</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8169999999999999</v>
+        <v>1.9663</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8239</v>
+        <v>1.9663</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5243</v>
+        <v>1.315</v>
       </c>
       <c r="K9" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="L9" t="n">
-        <v>244</v>
+        <v>106</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7004</v>
+        <v>3.2813</v>
       </c>
       <c r="N9" t="n">
-        <v>323</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.662</v>
+        <v>3.1131</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3764</v>
+        <v>0.4402</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6166</v>
+        <v>0.7674</v>
       </c>
       <c r="E10" t="n">
-        <v>2.662</v>
+        <v>3.1131</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4738</v>
+        <v>2.6624</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1882</v>
+        <v>0.4507</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4738</v>
+        <v>2.6624</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4862</v>
+        <v>2.7719</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1882</v>
+        <v>0.4507</v>
       </c>
       <c r="K10" t="n">
         <v>76</v>
@@ -897,7 +897,7 @@
         <v>57</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6744</v>
+        <v>3.2226</v>
       </c>
       <c r="N10" t="n">
         <v>133</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Forester</t>
+          <t>Krad</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5629</v>
+        <v>3.044</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3624</v>
+        <v>0.4304</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.7362</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5629</v>
+        <v>3.044</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6622</v>
+        <v>1.0312</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0993</v>
+        <v>2.0127</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6622</v>
+        <v>1.0312</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1578</v>
+        <v>0.5362</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0993</v>
+        <v>2.0127</v>
       </c>
       <c r="K11" t="n">
         <v>93</v>
@@ -943,7 +943,7 @@
         <v>175</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0585</v>
+        <v>2.5489</v>
       </c>
       <c r="N11" t="n">
         <v>268</v>
@@ -952,81 +952,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lack1</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4694</v>
+        <v>2.8099</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3492</v>
+        <v>0.3973</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5399</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4694</v>
+        <v>2.8099</v>
       </c>
       <c r="F12" t="n">
-        <v>3.176</v>
+        <v>-0.4302</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7066</v>
+        <v>3.2401</v>
       </c>
       <c r="H12" t="n">
-        <v>3.176</v>
+        <v>-0.4302</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5742</v>
+        <v>-0.4479</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7066</v>
+        <v>3.2401</v>
       </c>
       <c r="K12" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="L12" t="n">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8676</v>
+        <v>2.7922</v>
       </c>
       <c r="N12" t="n">
-        <v>268</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Krad</t>
+          <t>Lack1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4528</v>
+        <v>2.4328</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3468</v>
+        <v>0.344</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5333</v>
+        <v>0.4603</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4528</v>
+        <v>2.4328</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1606</v>
+        <v>3.1353</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2922</v>
+        <v>-0.7025</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1606</v>
+        <v>5.5607</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1302</v>
+        <v>2.8913</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2922</v>
+        <v>-0.7025</v>
       </c>
       <c r="K13" t="n">
         <v>93</v>
@@ -1035,7 +1035,7 @@
         <v>175</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4224</v>
+        <v>2.1888</v>
       </c>
       <c r="N13" t="n">
         <v>268</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8965</v>
+        <v>2.3464</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2682</v>
+        <v>0.3318</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3117</v>
+        <v>0.4213</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8965</v>
+        <v>2.3464</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2443</v>
+        <v>2.483</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3478</v>
+        <v>-0.1366</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2443</v>
+        <v>3.2624</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8191</v>
+        <v>1.6963</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3478</v>
+        <v>-0.1366</v>
       </c>
       <c r="K14" t="n">
         <v>89</v>
@@ -1081,7 +1081,7 @@
         <v>49</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4713</v>
+        <v>1.5597</v>
       </c>
       <c r="N14" t="n">
         <v>138</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REDSTAR</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1336</v>
+        <v>1.6376</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1603</v>
+        <v>0.2316</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0077</v>
+        <v>0.1013</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1336</v>
+        <v>1.6376</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3164</v>
+        <v>2.1885</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1828</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3164</v>
+        <v>2.2244</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3164</v>
+        <v>1.1566</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1828</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L15" t="n">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1336</v>
+        <v>0.6057000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>194</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0973</v>
+        <v>1.4388</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1552</v>
+        <v>0.2035</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0067</v>
+        <v>0.0115</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0973</v>
+        <v>1.4388</v>
       </c>
       <c r="F16" t="n">
-        <v>1.719</v>
+        <v>1.8112</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6217</v>
+        <v>-0.3724</v>
       </c>
       <c r="H16" t="n">
-        <v>1.719</v>
+        <v>1.8112</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7335</v>
+        <v>1.8857</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6217</v>
+        <v>-0.3724</v>
       </c>
       <c r="K16" t="n">
         <v>76</v>
@@ -1173,7 +1173,7 @@
         <v>57</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1118</v>
+        <v>1.5133</v>
       </c>
       <c r="N16" t="n">
         <v>133</v>
@@ -1182,323 +1182,323 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9973</v>
+        <v>1.3516</v>
       </c>
       <c r="C17" t="n">
-        <v>0.141</v>
+        <v>0.1911</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0466</v>
+        <v>-0.0278</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9973</v>
+        <v>1.3516</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3956</v>
+        <v>0.8603</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6017</v>
+        <v>0.4913</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3956</v>
+        <v>0.8603</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3989</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6017</v>
+        <v>0.4913</v>
       </c>
       <c r="K17" t="n">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="L17" t="n">
-        <v>69</v>
+        <v>244</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0006</v>
+        <v>1.387</v>
       </c>
       <c r="N17" t="n">
-        <v>171</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mopoz</t>
+          <t>REDSTAR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9966</v>
+        <v>1.2118</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1409</v>
+        <v>0.1714</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0469</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9966</v>
+        <v>1.2118</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6828</v>
+        <v>1.3923</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3138</v>
+        <v>-0.1805</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6828</v>
+        <v>1.3923</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6885</v>
+        <v>1.3923</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3138</v>
+        <v>-0.1805</v>
       </c>
       <c r="K18" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="L18" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0023</v>
+        <v>1.2118</v>
       </c>
       <c r="N18" t="n">
-        <v>133</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>forsyy</t>
+          <t>mopoz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8269</v>
+        <v>1.2012</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1169</v>
+        <v>0.1699</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1145</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8269</v>
+        <v>1.2012</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4689</v>
+        <v>0.8356</v>
       </c>
       <c r="G19" t="n">
-        <v>0.358</v>
+        <v>0.3656</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4689</v>
+        <v>0.8356</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4728</v>
+        <v>0.87</v>
       </c>
       <c r="J19" t="n">
-        <v>0.358</v>
+        <v>0.3656</v>
       </c>
       <c r="K19" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="L19" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8308</v>
+        <v>1.2356</v>
       </c>
       <c r="N19" t="n">
-        <v>171</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.9469</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0843</v>
+        <v>0.1339</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2063</v>
+        <v>-0.2105</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.9469</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4365</v>
+        <v>0.5874</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8401999999999999</v>
+        <v>0.3595</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4365</v>
+        <v>0.5874</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1643</v>
+        <v>0.6116</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8401999999999999</v>
+        <v>0.3595</v>
       </c>
       <c r="K20" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="L20" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3240999999999999</v>
+        <v>0.9711000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>138</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SHiPZ</t>
+          <t>forsyy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5603</v>
+        <v>0.7778</v>
       </c>
       <c r="C21" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2207</v>
+        <v>-0.2869</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5603</v>
+        <v>0.7778</v>
       </c>
       <c r="F21" t="n">
-        <v>0.199</v>
+        <v>0.4812</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3613</v>
+        <v>0.2966</v>
       </c>
       <c r="H21" t="n">
-        <v>0.199</v>
+        <v>0.4812</v>
       </c>
       <c r="I21" t="n">
-        <v>0.199</v>
+        <v>0.501</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3613</v>
+        <v>0.2966</v>
       </c>
       <c r="K21" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="L21" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5603</v>
+        <v>0.7976</v>
       </c>
       <c r="N21" t="n">
-        <v>194</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NEOFRAG</t>
+          <t>SHiPZ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2464</v>
+        <v>0.6882</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0348</v>
+        <v>0.0973</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3457</v>
+        <v>-0.3273</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2464</v>
+        <v>0.6882</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2464</v>
+        <v>0.3236</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.3646</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2464</v>
+        <v>0.3236</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2464</v>
+        <v>0.3236</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.3646</v>
       </c>
       <c r="K22" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2464</v>
+        <v>0.6881999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>67</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1342</v>
+        <v>0.4576</v>
       </c>
       <c r="C23" t="n">
-        <v>0.019</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3904</v>
+        <v>-0.4314</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1342</v>
+        <v>0.4576</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6107</v>
+        <v>1.0051</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4765</v>
+        <v>-0.5475</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6107</v>
+        <v>1.0051</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6158</v>
+        <v>0.5226</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4765</v>
+        <v>-0.5475</v>
       </c>
       <c r="K23" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="L23" t="n">
-        <v>244</v>
+        <v>49</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1393</v>
+        <v>-0.02490000000000003</v>
       </c>
       <c r="N23" t="n">
-        <v>323</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0029</v>
+        <v>0.3034</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0004</v>
+        <v>0.0429</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4428</v>
+        <v>-0.501</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0029</v>
+        <v>0.3034</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0029</v>
+        <v>0.3034</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0029</v>
+        <v>0.3034</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0029</v>
+        <v>0.3034</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0029</v>
+        <v>0.3034</v>
       </c>
       <c r="N24" t="n">
         <v>80</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>NEOFRAG</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1949</v>
+        <v>0.2566</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0276</v>
+        <v>0.0363</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5216</v>
+        <v>-0.5222</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1949</v>
+        <v>0.2566</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5735</v>
+        <v>0.2566</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7684</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5735</v>
+        <v>0.2566</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4648</v>
+        <v>0.2566</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7684</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L25" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3036</v>
+        <v>0.2566</v>
       </c>
       <c r="N25" t="n">
-        <v>138</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>SHOCK</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2482</v>
+        <v>-0.0631</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0351</v>
+        <v>-0.0089</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.6665</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2482</v>
+        <v>-0.0631</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.226</v>
+        <v>-0.0631</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0222</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.226</v>
+        <v>-0.0631</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1832</v>
+        <v>-0.0631</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0222</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L26" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2054</v>
+        <v>-0.0631</v>
       </c>
       <c r="N26" t="n">
-        <v>138</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2608</v>
+        <v>-0.074</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0369</v>
+        <v>-0.0105</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5478</v>
+        <v>-0.6714</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2608</v>
+        <v>-0.074</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2608</v>
+        <v>-0.074</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2608</v>
+        <v>-0.074</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2608</v>
+        <v>-0.074</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2608</v>
+        <v>-0.074</v>
       </c>
       <c r="N27" t="n">
         <v>80</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SHOCK</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3882</v>
+        <v>-0.1595</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0549</v>
+        <v>-0.0226</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5986</v>
+        <v>-0.71</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3882</v>
+        <v>-0.1595</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3882</v>
+        <v>-0.2829</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.1234</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3882</v>
+        <v>-0.2829</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3882</v>
+        <v>-0.1471</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.1234</v>
       </c>
       <c r="K28" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3882</v>
+        <v>-0.02370000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>67</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pechyn</t>
+          <t>manguss</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.58</v>
+        <v>-0.2424</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.082</v>
+        <v>-0.0343</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.675</v>
+        <v>-0.7474</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.58</v>
+        <v>-0.2424</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.58</v>
+        <v>0.2553</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.4977</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.58</v>
+        <v>0.2553</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.58</v>
+        <v>0.2658</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.4977</v>
       </c>
       <c r="K29" t="n">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.58</v>
+        <v>-0.2319</v>
       </c>
       <c r="N29" t="n">
-        <v>80</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>manguss</t>
+          <t>Pechyn</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6127</v>
+        <v>-0.3936</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0866</v>
+        <v>-0.0557</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.8157</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6127</v>
+        <v>-0.3936</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0772</v>
+        <v>-0.3936</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6899</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0772</v>
+        <v>-0.3936</v>
       </c>
       <c r="I30" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.3936</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6899</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="L30" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6121</v>
+        <v>-0.3936</v>
       </c>
       <c r="N30" t="n">
-        <v>171</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6319</v>
+        <v>-0.3991</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.0564</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6957</v>
+        <v>-0.8182</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6319</v>
+        <v>-0.3991</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3681</v>
+        <v>0.6009</v>
       </c>
       <c r="G31" t="n">
         <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3681</v>
+        <v>0.6009</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3712</v>
+        <v>0.6256</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>69</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6288</v>
+        <v>-0.3744</v>
       </c>
       <c r="N31" t="n">
         <v>171</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6565</v>
+        <v>-0.476</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.0673</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7055</v>
+        <v>-0.8529</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6565</v>
+        <v>-0.476</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4988</v>
+        <v>-0.476</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1577</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4988</v>
+        <v>-0.476</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4043</v>
+        <v>-0.476</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.1577</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L32" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.476</v>
       </c>
       <c r="N32" t="n">
-        <v>138</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8719</v>
+        <v>-0.5569</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1233</v>
+        <v>-0.0788</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7913</v>
+        <v>-0.8894</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8719</v>
+        <v>-0.5569</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8719</v>
+        <v>-0.5569</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8719</v>
+        <v>-0.5569</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8719</v>
+        <v>-0.5569</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8719</v>
+        <v>-0.5569</v>
       </c>
       <c r="N33" t="n">
         <v>80</v>
@@ -1964,139 +1964,139 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9655</v>
+        <v>-0.6044</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1365</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8286</v>
+        <v>-0.9109</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9655</v>
+        <v>-0.6044</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9655</v>
+        <v>-0.5345</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.0699</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9655</v>
+        <v>-0.5345</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9655</v>
+        <v>-0.2779</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.0699</v>
       </c>
       <c r="K34" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9655</v>
+        <v>-0.3478</v>
       </c>
       <c r="N34" t="n">
-        <v>67</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>beastik</t>
+          <t>sAvana1</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0508</v>
+        <v>-0.7413</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1486</v>
+        <v>-0.1048</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8625</v>
+        <v>-0.9727</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0508</v>
+        <v>-0.7413</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0508</v>
+        <v>-0.7413</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0508</v>
+        <v>-0.7413</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0508</v>
+        <v>-0.7413</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0508</v>
+        <v>-0.7413</v>
       </c>
       <c r="N35" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sAvana1</t>
+          <t>beastik</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1094</v>
+        <v>-0.9292</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1569</v>
+        <v>-0.1314</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8859</v>
+        <v>-1.0575</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1094</v>
+        <v>-0.9292</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1094</v>
+        <v>-0.9292</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1094</v>
+        <v>-0.9292</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1094</v>
+        <v>-0.9292</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1094</v>
+        <v>-0.9292</v>
       </c>
       <c r="N36" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37">
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.5054</v>
+        <v>-1.0236</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2129</v>
+        <v>-0.1447</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0437</v>
+        <v>-1.1001</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.5054</v>
+        <v>-1.0236</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4295</v>
+        <v>0.6025</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.9349</v>
+        <v>-1.6261</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4295</v>
+        <v>0.6025</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4295</v>
+        <v>0.6025</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.9349</v>
+        <v>-1.6261</v>
       </c>
       <c r="K37" t="n">
         <v>88</v>
@@ -2139,7 +2139,7 @@
         <v>106</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.5054</v>
+        <v>-1.0236</v>
       </c>
       <c r="N37" t="n">
         <v>194</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ZEDKO</t>
+          <t>dream3r</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.781</v>
+        <v>-1.1968</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2518</v>
+        <v>-0.1692</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1535</v>
+        <v>-1.1783</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.781</v>
+        <v>-1.1968</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.781</v>
+        <v>0.0603</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-1.2571</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.781</v>
+        <v>0.0603</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.781</v>
+        <v>0.0603</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-1.2571</v>
       </c>
       <c r="K38" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.781</v>
+        <v>-1.1968</v>
       </c>
       <c r="N38" t="n">
-        <v>67</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dream3r</t>
+          <t>ZEDKO</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.8735</v>
+        <v>-1.3914</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2649</v>
+        <v>-0.1968</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1903</v>
+        <v>-1.2662</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.8735</v>
+        <v>-1.3914</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.306</v>
+        <v>-1.3914</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.5675</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.306</v>
+        <v>-1.3914</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.306</v>
+        <v>-1.3914</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.5675</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="L39" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8735</v>
+        <v>-1.3914</v>
       </c>
       <c r="N39" t="n">
-        <v>194</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0862</v>
+        <v>-1.6666</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.295</v>
+        <v>-0.2357</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2751</v>
+        <v>-1.3904</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0862</v>
+        <v>-1.6666</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8547</v>
+        <v>-1.5515</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.2315</v>
+        <v>-0.1151</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8547</v>
+        <v>-1.5515</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.8703</v>
+        <v>-1.6153</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.2315</v>
+        <v>-0.1151</v>
       </c>
       <c r="K40" t="n">
         <v>102</v>
@@ -2277,7 +2277,7 @@
         <v>69</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.1018</v>
+        <v>-1.7304</v>
       </c>
       <c r="N40" t="n">
         <v>171</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.5618</v>
+        <v>-1.8083</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3623</v>
+        <v>-0.2557</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4645</v>
+        <v>-1.4544</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.5618</v>
+        <v>-1.8083</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6316</v>
+        <v>-1.2062</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9302</v>
+        <v>-0.6021</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6316</v>
+        <v>-1.2062</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6453</v>
+        <v>-1.2558</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9302</v>
+        <v>-0.6021</v>
       </c>
       <c r="K41" t="n">
         <v>76</v>
@@ -2323,7 +2323,7 @@
         <v>57</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.5755</v>
+        <v>-1.8579</v>
       </c>
       <c r="N41" t="n">
         <v>133</v>
@@ -2429,10 +2429,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0373</v>
+        <v>1.0331</v>
       </c>
       <c r="J2" t="n">
-        <v>26.9698</v>
+        <v>26.8606</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.32</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7887</v>
+        <v>0.8193</v>
       </c>
       <c r="J3" t="n">
-        <v>20.5062</v>
+        <v>21.3018</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.28</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6761</v>
+        <v>0.7316</v>
       </c>
       <c r="J4" t="n">
-        <v>17.5786</v>
+        <v>19.0216</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.22</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5158</v>
+        <v>0.5938</v>
       </c>
       <c r="J5" t="n">
-        <v>13.4108</v>
+        <v>15.4388</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3623</v>
+        <v>0.445</v>
       </c>
       <c r="J6" t="n">
-        <v>9.4198</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0672</v>
+        <v>0.0313</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7472</v>
+        <v>0.8138</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.116</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.016</v>
+        <v>-2.5636</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.85</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2579</v>
+        <v>-0.1728</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.7054</v>
+        <v>-4.4928</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.78</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3744</v>
+        <v>-0.2423</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.734400000000001</v>
+        <v>-6.2998</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.78</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3744</v>
+        <v>-0.2423</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.734400000000001</v>
+        <v>-6.2998</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.56</v>
       </c>
       <c r="I12" t="n">
-        <v>1.304</v>
+        <v>1.1993</v>
       </c>
       <c r="J12" t="n">
-        <v>36.512</v>
+        <v>33.5804</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9759</v>
+        <v>0.9868</v>
       </c>
       <c r="J13" t="n">
-        <v>27.3252</v>
+        <v>27.6304</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.38</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9318</v>
+        <v>0.9495</v>
       </c>
       <c r="J14" t="n">
-        <v>26.0904</v>
+        <v>26.586</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.6187</v>
       </c>
       <c r="J15" t="n">
-        <v>15.2572</v>
+        <v>17.3236</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7235</v>
+        <v>-0.6665</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.258</v>
+        <v>-18.662</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4113</v>
+        <v>0.464</v>
       </c>
       <c r="J17" t="n">
-        <v>11.5164</v>
+        <v>12.992</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3035</v>
+        <v>0.3209</v>
       </c>
       <c r="J18" t="n">
-        <v>8.497999999999999</v>
+        <v>8.985200000000001</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.88</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1799</v>
+        <v>-0.1405</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.0372</v>
+        <v>-3.934</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.71</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4707</v>
+        <v>-0.3074</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.1796</v>
+        <v>-8.607200000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.35</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.6387</v>
       </c>
       <c r="J21" t="n">
-        <v>-25.6704</v>
+        <v>-17.8836</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3904</v>
+        <v>0.3376</v>
       </c>
       <c r="J22" t="n">
-        <v>11.3216</v>
+        <v>9.7904</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.08</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2163</v>
+        <v>0.1691</v>
       </c>
       <c r="J23" t="n">
-        <v>6.2727</v>
+        <v>4.9039</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2053</v>
+        <v>-0.1278</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.9537</v>
+        <v>-3.7062</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.77</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4119</v>
+        <v>-0.2616</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.9451</v>
+        <v>-7.5864</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.76</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4261</v>
+        <v>-0.2714</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.3569</v>
+        <v>-7.8706</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.57</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7981</v>
+        <v>0.714</v>
       </c>
       <c r="J27" t="n">
-        <v>23.1449</v>
+        <v>20.706</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4741</v>
+        <v>0.4081</v>
       </c>
       <c r="J28" t="n">
-        <v>13.7489</v>
+        <v>11.8349</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.13</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2086</v>
+        <v>0.1993</v>
       </c>
       <c r="J29" t="n">
-        <v>6.0494</v>
+        <v>5.7797</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.263</v>
+        <v>-0.1495</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.627</v>
+        <v>-4.3355</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.397</v>
+        <v>-0.2443</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.513</v>
+        <v>-7.0847</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0992</v>
+        <v>0.0469</v>
       </c>
       <c r="J32" t="n">
-        <v>2.2816</v>
+        <v>1.0787</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.91</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0988</v>
+        <v>-0.0977</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.2724</v>
+        <v>-2.2471</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.84</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2203</v>
+        <v>-0.1749</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.0669</v>
+        <v>-4.0227</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2917</v>
+        <v>-0.2148</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.7091</v>
+        <v>-4.9404</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8526</v>
+        <v>-0.5877</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.6098</v>
+        <v>-13.5171</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.76</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9539</v>
+        <v>0.8727</v>
       </c>
       <c r="J37" t="n">
-        <v>21.9397</v>
+        <v>20.0721</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.4</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5496</v>
+        <v>0.4964</v>
       </c>
       <c r="J38" t="n">
-        <v>12.6408</v>
+        <v>11.4172</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.28</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3732</v>
+        <v>0.3657</v>
       </c>
       <c r="J39" t="n">
-        <v>8.583600000000001</v>
+        <v>8.411099999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.16</v>
       </c>
       <c r="I40" t="n">
-        <v>0.201</v>
+        <v>0.2204</v>
       </c>
       <c r="J40" t="n">
-        <v>4.623</v>
+        <v>5.0692</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.96</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1889</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.3447</v>
+        <v>-2.1574</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.05</v>
       </c>
       <c r="I42" t="n">
-        <v>1.9944</v>
+        <v>1.6973</v>
       </c>
       <c r="J42" t="n">
-        <v>39.888</v>
+        <v>33.946</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>2.05</v>
       </c>
       <c r="I43" t="n">
-        <v>1.9944</v>
+        <v>1.6973</v>
       </c>
       <c r="J43" t="n">
-        <v>39.888</v>
+        <v>33.946</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.43</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8541</v>
+        <v>0.9908</v>
       </c>
       <c r="J44" t="n">
-        <v>17.082</v>
+        <v>19.816</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.24</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4526</v>
+        <v>0.5773</v>
       </c>
       <c r="J45" t="n">
-        <v>9.052</v>
+        <v>11.546</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.22</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4078</v>
+        <v>0.5291</v>
       </c>
       <c r="J46" t="n">
-        <v>8.156000000000001</v>
+        <v>10.582</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.07</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4413</v>
+        <v>0.5977</v>
       </c>
       <c r="J47" t="n">
-        <v>8.826000000000001</v>
+        <v>11.954</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.4</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.7644</v>
+        <v>-0.5325</v>
       </c>
       <c r="J48" t="n">
-        <v>-15.288</v>
+        <v>-10.65</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.36</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.8243</v>
+        <v>-0.5719</v>
       </c>
       <c r="J49" t="n">
-        <v>-16.486</v>
+        <v>-11.438</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.33</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8673</v>
+        <v>-0.6019</v>
       </c>
       <c r="J50" t="n">
-        <v>-17.346</v>
+        <v>-12.038</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.2</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0414</v>
+        <v>-0.7353</v>
       </c>
       <c r="J51" t="n">
-        <v>-20.828</v>
+        <v>-14.706</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.57</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3766</v>
+        <v>0.9663</v>
       </c>
       <c r="J52" t="n">
-        <v>38.5448</v>
+        <v>27.0564</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.35</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9247</v>
+        <v>0.6786</v>
       </c>
       <c r="J53" t="n">
-        <v>25.8916</v>
+        <v>19.0008</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.163</v>
+        <v>0.2231</v>
       </c>
       <c r="J54" t="n">
-        <v>4.564</v>
+        <v>6.2468</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.93</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3791</v>
+        <v>-0.3053</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.6148</v>
+        <v>-8.548400000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.91</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4375</v>
+        <v>-0.3656</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.25</v>
+        <v>-10.2368</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.12</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2912</v>
+        <v>0.311</v>
       </c>
       <c r="J57" t="n">
-        <v>8.153600000000001</v>
+        <v>8.708</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1049</v>
+        <v>-0.0814</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.9372</v>
+        <v>-2.2792</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.175</v>
+        <v>-0.115</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.9</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.89</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2142</v>
+        <v>-0.1366</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.9976</v>
+        <v>-3.8248</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4492</v>
+        <v>-0.2883</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.5776</v>
+        <v>-8.0724</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.62</v>
       </c>
       <c r="I62" t="n">
-        <v>1.3388</v>
+        <v>0.9655</v>
       </c>
       <c r="J62" t="n">
-        <v>28.1148</v>
+        <v>20.2755</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.6</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2999</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>27.2979</v>
+        <v>19.782</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.56</v>
       </c>
       <c r="I64" t="n">
-        <v>1.2202</v>
+        <v>0.8949</v>
       </c>
       <c r="J64" t="n">
-        <v>25.6242</v>
+        <v>18.7929</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.32</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6725</v>
+        <v>0.6028</v>
       </c>
       <c r="J65" t="n">
-        <v>14.1225</v>
+        <v>12.6588</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3274</v>
+        <v>0.3925</v>
       </c>
       <c r="J66" t="n">
-        <v>6.8754</v>
+        <v>8.2425</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.84</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1668</v>
+        <v>-0.1529</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.5028</v>
+        <v>-3.2109</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.82</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.199</v>
+        <v>-0.175</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.179</v>
+        <v>-3.675</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.65</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.493</v>
+        <v>-0.3403</v>
       </c>
       <c r="J69" t="n">
-        <v>-10.353</v>
+        <v>-7.1463</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.54</v>
+        <v>-0.368</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.34</v>
+        <v>-7.728</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.49</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7207</v>
+        <v>-0.4895</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.1347</v>
+        <v>-10.2795</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.8</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.2216</v>
+        <v>-0.1919</v>
       </c>
       <c r="J72" t="n">
-        <v>-4.6536</v>
+        <v>-4.0299</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.72</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.3488</v>
+        <v>-0.2739</v>
       </c>
       <c r="J73" t="n">
-        <v>-7.3248</v>
+        <v>-5.7519</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.63</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.5148</v>
+        <v>-0.356</v>
       </c>
       <c r="J74" t="n">
-        <v>-10.8108</v>
+        <v>-7.476</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.6</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5615</v>
+        <v>-0.3836</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.7915</v>
+        <v>-8.0556</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5911</v>
+        <v>-0.4022</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.4131</v>
+        <v>-8.446199999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.22</v>
       </c>
       <c r="I77" t="n">
-        <v>2.0789</v>
+        <v>1.6485</v>
       </c>
       <c r="J77" t="n">
-        <v>43.6569</v>
+        <v>34.6185</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.67</v>
       </c>
       <c r="I78" t="n">
-        <v>1.4409</v>
+        <v>1.0265</v>
       </c>
       <c r="J78" t="n">
-        <v>30.2589</v>
+        <v>21.5565</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.32</v>
       </c>
       <c r="I79" t="n">
-        <v>0.679</v>
+        <v>0.6047</v>
       </c>
       <c r="J79" t="n">
-        <v>14.259</v>
+        <v>12.6987</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.22</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4513</v>
+        <v>0.4678</v>
       </c>
       <c r="J80" t="n">
-        <v>9.4773</v>
+        <v>9.8238</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8657</v>
+        <v>-0.8242</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.1797</v>
+        <v>-17.3082</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.28</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4926</v>
+        <v>0.4794</v>
       </c>
       <c r="J82" t="n">
-        <v>13.7928</v>
+        <v>13.4232</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2433</v>
+        <v>0.2656</v>
       </c>
       <c r="J83" t="n">
-        <v>6.8124</v>
+        <v>7.4368</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.08</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1911</v>
+        <v>0.204</v>
       </c>
       <c r="J84" t="n">
-        <v>5.3508</v>
+        <v>5.712</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2787</v>
+        <v>-0.1673</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.8036</v>
+        <v>-4.6844</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.68</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5468</v>
+        <v>-0.3556</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.3104</v>
+        <v>-9.956799999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.58</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3908</v>
+        <v>0.976</v>
       </c>
       <c r="J87" t="n">
-        <v>38.9424</v>
+        <v>27.328</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.46</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1532</v>
+        <v>0.822</v>
       </c>
       <c r="J88" t="n">
-        <v>32.2896</v>
+        <v>23.016</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.28</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.5814</v>
       </c>
       <c r="J89" t="n">
-        <v>21.2408</v>
+        <v>16.2792</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.97</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2524</v>
+        <v>-0.1759</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.0672</v>
+        <v>-4.9252</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.1803</v>
+        <v>-1.1799</v>
       </c>
       <c r="J91" t="n">
-        <v>-33.0484</v>
+        <v>-33.0372</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.3</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4959</v>
+        <v>0.4859</v>
       </c>
       <c r="J92" t="n">
-        <v>13.8852</v>
+        <v>13.6052</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4009</v>
+        <v>0.4148</v>
       </c>
       <c r="J93" t="n">
-        <v>11.2252</v>
+        <v>11.6144</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.22</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3868</v>
+        <v>0.4044</v>
       </c>
       <c r="J94" t="n">
-        <v>10.8304</v>
+        <v>11.3232</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0227</v>
+        <v>0.0558</v>
       </c>
       <c r="J95" t="n">
-        <v>0.6356000000000001</v>
+        <v>1.5624</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6556</v>
+        <v>-0.4364</v>
       </c>
       <c r="J96" t="n">
-        <v>-18.3568</v>
+        <v>-12.2192</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.24</v>
       </c>
       <c r="I97" t="n">
-        <v>0.736</v>
+        <v>0.5504</v>
       </c>
       <c r="J97" t="n">
-        <v>20.608</v>
+        <v>15.4112</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5058</v>
+        <v>0.4142</v>
       </c>
       <c r="J98" t="n">
-        <v>14.1624</v>
+        <v>11.5976</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.11</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3916</v>
+        <v>0.3499</v>
       </c>
       <c r="J99" t="n">
-        <v>10.9648</v>
+        <v>9.7972</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.96</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2315</v>
+        <v>-0.1774</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.482</v>
+        <v>-4.9672</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.79</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7107</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="J101" t="n">
-        <v>-19.8996</v>
+        <v>-18.5304</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8014</v>
+        <v>0.7307</v>
       </c>
       <c r="J102" t="n">
-        <v>23.2406</v>
+        <v>21.1903</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.98</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0621</v>
+        <v>-0.0352</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.8009</v>
+        <v>-1.0208</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.97</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0871</v>
+        <v>-0.0492</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.5259</v>
+        <v>-1.4268</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.87</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2746</v>
+        <v>-0.1657</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.9634</v>
+        <v>-4.8053</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.6</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6444</v>
+        <v>-0.4282</v>
       </c>
       <c r="J106" t="n">
-        <v>-18.6876</v>
+        <v>-12.4178</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.43</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1636</v>
+        <v>0.8216</v>
       </c>
       <c r="J107" t="n">
-        <v>33.7444</v>
+        <v>23.8264</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.19</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6179</v>
+        <v>0.478</v>
       </c>
       <c r="J108" t="n">
-        <v>17.9191</v>
+        <v>13.862</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.97</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1888</v>
+        <v>-0.14</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.4752</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.9</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4169</v>
+        <v>-0.3604</v>
       </c>
       <c r="J110" t="n">
-        <v>-12.0901</v>
+        <v>-10.4516</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.71</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.8605</v>
       </c>
       <c r="J111" t="n">
-        <v>-25.9463</v>
+        <v>-24.9545</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6422</v>
+        <v>0.4899</v>
       </c>
       <c r="J112" t="n">
-        <v>17.9816</v>
+        <v>13.7172</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1983</v>
+        <v>0.1524</v>
       </c>
       <c r="J113" t="n">
-        <v>5.5524</v>
+        <v>4.2672</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.8</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3682</v>
+        <v>-0.2318</v>
       </c>
       <c r="J114" t="n">
-        <v>-10.3096</v>
+        <v>-6.4904</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.78</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3975</v>
+        <v>-0.2517</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.13</v>
+        <v>-7.0476</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.67</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.3576</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.3412</v>
+        <v>-10.0128</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.63</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8528</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="J117" t="n">
-        <v>23.8784</v>
+        <v>16.5256</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.29</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4483</v>
+        <v>0.3672</v>
       </c>
       <c r="J118" t="n">
-        <v>12.5524</v>
+        <v>10.2816</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.27</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4208</v>
+        <v>0.3533</v>
       </c>
       <c r="J119" t="n">
-        <v>11.7824</v>
+        <v>9.8924</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.87</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3166</v>
+        <v>-0.186</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.864800000000001</v>
+        <v>-5.208</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3606</v>
+        <v>-0.2175</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.0968</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.54</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2072</v>
+        <v>0.8789</v>
       </c>
       <c r="J122" t="n">
-        <v>22.9368</v>
+        <v>16.6991</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.49</v>
       </c>
       <c r="I123" t="n">
-        <v>1.1042</v>
+        <v>0.8185</v>
       </c>
       <c r="J123" t="n">
-        <v>20.9798</v>
+        <v>15.5515</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.48</v>
       </c>
       <c r="I124" t="n">
-        <v>1.083</v>
+        <v>0.8064</v>
       </c>
       <c r="J124" t="n">
-        <v>20.577</v>
+        <v>15.3216</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.32</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6969</v>
+        <v>0.6092</v>
       </c>
       <c r="J125" t="n">
-        <v>13.2411</v>
+        <v>11.5748</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.16</v>
       </c>
       <c r="I126" t="n">
-        <v>0.3195</v>
+        <v>0.3843</v>
       </c>
       <c r="J126" t="n">
-        <v>6.0705</v>
+        <v>7.3017</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1304</v>
+        <v>0.0983</v>
       </c>
       <c r="J127" t="n">
-        <v>2.4776</v>
+        <v>1.8677</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.9</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0839</v>
+        <v>-0.0934</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.5941</v>
+        <v>-1.7746</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.76</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3157</v>
+        <v>-0.2444</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.9983</v>
+        <v>-4.6436</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.7</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4316</v>
+        <v>-0.2995</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.2004</v>
+        <v>-5.6905</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.24</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.0273</v>
+        <v>-0.7268</v>
       </c>
       <c r="J131" t="n">
-        <v>-19.5187</v>
+        <v>-13.8092</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.01</v>
       </c>
       <c r="I132" t="n">
-        <v>1.9323</v>
+        <v>1.4643</v>
       </c>
       <c r="J132" t="n">
-        <v>42.5106</v>
+        <v>32.2146</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.25</v>
       </c>
       <c r="I133" t="n">
-        <v>0.597</v>
+        <v>0.5291</v>
       </c>
       <c r="J133" t="n">
-        <v>13.134</v>
+        <v>11.6402</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0863</v>
+        <v>0.1658</v>
       </c>
       <c r="J134" t="n">
-        <v>1.8986</v>
+        <v>3.6476</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0863</v>
+        <v>0.1658</v>
       </c>
       <c r="J135" t="n">
-        <v>1.8986</v>
+        <v>3.6476</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1488</v>
+        <v>-0.0672</v>
       </c>
       <c r="J136" t="n">
-        <v>-3.2736</v>
+        <v>-1.4784</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0576</v>
+        <v>-0.0673</v>
       </c>
       <c r="J137" t="n">
-        <v>-1.2672</v>
+        <v>-1.4806</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.88</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1672</v>
+        <v>-0.1373</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.6784</v>
+        <v>-3.0206</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2207</v>
+        <v>-0.1689</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.8554</v>
+        <v>-3.7158</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2207</v>
+        <v>-0.1689</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.8554</v>
+        <v>-3.7158</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.59</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.626</v>
+        <v>-0.4171</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.772</v>
+        <v>-9.1762</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.37</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9548</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="J142" t="n">
-        <v>28.644</v>
+        <v>28.563</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.27</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7248</v>
+        <v>0.7262</v>
       </c>
       <c r="J143" t="n">
-        <v>21.744</v>
+        <v>21.786</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.25</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6751</v>
+        <v>0.6793</v>
       </c>
       <c r="J144" t="n">
-        <v>20.253</v>
+        <v>20.379</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.18</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4699</v>
+        <v>0.5137</v>
       </c>
       <c r="J145" t="n">
-        <v>14.097</v>
+        <v>15.411</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5012</v>
+        <v>-0.4302</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.036</v>
+        <v>-12.906</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.11</v>
       </c>
       <c r="I147" t="n">
-        <v>0.2956</v>
+        <v>0.312</v>
       </c>
       <c r="J147" t="n">
-        <v>8.868</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1269</v>
+        <v>0.1008</v>
       </c>
       <c r="J148" t="n">
-        <v>3.807</v>
+        <v>3.024</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.84</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2762</v>
+        <v>-0.1828</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.286</v>
+        <v>-5.484</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.71</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4766</v>
+        <v>-0.3101</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.298</v>
+        <v>-9.303000000000001</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.367</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.74</v>
+        <v>-11.01</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0206</v>
+        <v>-0.0091</v>
       </c>
       <c r="J152" t="n">
-        <v>0.515</v>
+        <v>-0.2275</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0785</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.27</v>
+        <v>-1.9625</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.91</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1508</v>
+        <v>-0.1132</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.77</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.82</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3223</v>
+        <v>-0.2061</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.057499999999999</v>
+        <v>-5.1525</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3382</v>
+        <v>-0.2161</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.455</v>
+        <v>-5.4025</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5417</v>
+        <v>0.4652</v>
       </c>
       <c r="J157" t="n">
-        <v>13.5425</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3061</v>
+        <v>0.2561</v>
       </c>
       <c r="J158" t="n">
-        <v>7.6525</v>
+        <v>6.4025</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0163</v>
+        <v>0.0375</v>
       </c>
       <c r="J159" t="n">
-        <v>0.4075</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.97</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1248</v>
+        <v>-0.0592</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.12</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.96</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1454</v>
+        <v>-0.0726</v>
       </c>
       <c r="J161" t="n">
-        <v>-3.635</v>
+        <v>-1.815</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>2.03</v>
       </c>
       <c r="I162" t="n">
-        <v>2.0055</v>
+        <v>1.7125</v>
       </c>
       <c r="J162" t="n">
-        <v>40.11</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.37</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7931</v>
+        <v>0.9033</v>
       </c>
       <c r="J163" t="n">
-        <v>15.862</v>
+        <v>18.066</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.37</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7931</v>
+        <v>0.9033</v>
       </c>
       <c r="J164" t="n">
-        <v>15.862</v>
+        <v>18.066</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.21</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4291</v>
+        <v>0.5375</v>
       </c>
       <c r="J165" t="n">
-        <v>8.582000000000001</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.19</v>
       </c>
       <c r="I166" t="n">
-        <v>0.3816</v>
+        <v>0.4879</v>
       </c>
       <c r="J166" t="n">
-        <v>7.632</v>
+        <v>9.757999999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.04</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2317</v>
+        <v>0.2249</v>
       </c>
       <c r="J167" t="n">
-        <v>4.634</v>
+        <v>4.498</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.89</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1021</v>
+        <v>-0.1058</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.042</v>
+        <v>-2.116</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.62</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.5561</v>
+        <v>-0.3741</v>
       </c>
       <c r="J169" t="n">
-        <v>-11.122</v>
+        <v>-7.482</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.62</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5561</v>
+        <v>-0.3741</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.122</v>
+        <v>-7.482</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.44</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.793</v>
+        <v>-0.5421</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.86</v>
+        <v>-10.842</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.17</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3402</v>
+        <v>0.3835</v>
       </c>
       <c r="J172" t="n">
-        <v>12.2472</v>
+        <v>13.806</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3098</v>
+        <v>0.3455</v>
       </c>
       <c r="J173" t="n">
-        <v>11.1528</v>
+        <v>12.438</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.08</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1935</v>
+        <v>0.2054</v>
       </c>
       <c r="J174" t="n">
-        <v>6.966</v>
+        <v>7.3944</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.99</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0391</v>
+        <v>-0.0204</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.4076</v>
+        <v>-0.7344000000000001</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6455</v>
+        <v>-0.429</v>
       </c>
       <c r="J176" t="n">
-        <v>-23.238</v>
+        <v>-15.444</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.32</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9352</v>
+        <v>0.9085</v>
       </c>
       <c r="J177" t="n">
-        <v>33.6672</v>
+        <v>32.706</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5746</v>
+        <v>0.5316</v>
       </c>
       <c r="J178" t="n">
-        <v>20.6856</v>
+        <v>19.1376</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.01</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0316</v>
+        <v>0.0493</v>
       </c>
       <c r="J179" t="n">
-        <v>1.1376</v>
+        <v>1.7748</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5493</v>
+        <v>-0.4962</v>
       </c>
       <c r="J180" t="n">
-        <v>-19.7748</v>
+        <v>-17.8632</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.78</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7266</v>
+        <v>-0.6806</v>
       </c>
       <c r="J181" t="n">
-        <v>-26.1576</v>
+        <v>-24.5016</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.27</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4672</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>12.6144</v>
+        <v>14.8743</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.02</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0376</v>
+        <v>0.0612</v>
       </c>
       <c r="J183" t="n">
-        <v>1.0152</v>
+        <v>1.6524</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.99</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0601</v>
+        <v>-0.024</v>
       </c>
       <c r="J184" t="n">
-        <v>-1.6227</v>
+        <v>-0.648</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.97</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1085</v>
+        <v>-0.0539</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.9295</v>
+        <v>-1.4553</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.95</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1498</v>
+        <v>-0.08</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.0446</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.21</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6309</v>
+        <v>0.6075</v>
       </c>
       <c r="J187" t="n">
-        <v>17.0343</v>
+        <v>16.4025</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4415</v>
+        <v>0.4289</v>
       </c>
       <c r="J188" t="n">
-        <v>11.9205</v>
+        <v>11.5803</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.08</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2358</v>
+        <v>0.2671</v>
       </c>
       <c r="J189" t="n">
-        <v>6.3666</v>
+        <v>7.2117</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.05</v>
       </c>
       <c r="I190" t="n">
-        <v>0.134</v>
+        <v>0.1762</v>
       </c>
       <c r="J190" t="n">
-        <v>3.618</v>
+        <v>4.7574</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.03</v>
       </c>
       <c r="I191" t="n">
-        <v>0.0617</v>
+        <v>0.109</v>
       </c>
       <c r="J191" t="n">
-        <v>1.6659</v>
+        <v>2.943</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.07</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3138</v>
+        <v>0.3392</v>
       </c>
       <c r="J192" t="n">
-        <v>5.9622</v>
+        <v>6.4448</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.84</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1597</v>
+        <v>-0.149</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.0343</v>
+        <v>-2.831</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.51</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.6901</v>
+        <v>-0.4684</v>
       </c>
       <c r="J194" t="n">
-        <v>-13.1119</v>
+        <v>-8.8996</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.49</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.7167</v>
+        <v>-0.4871</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.6173</v>
+        <v>-9.254899999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.44</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7814</v>
+        <v>-0.5341</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.8466</v>
+        <v>-10.1479</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.99</v>
       </c>
       <c r="I197" t="n">
-        <v>1.9525</v>
+        <v>1.6533</v>
       </c>
       <c r="J197" t="n">
-        <v>37.0975</v>
+        <v>31.4127</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.6</v>
       </c>
       <c r="I198" t="n">
-        <v>1.2809</v>
+        <v>1.2104</v>
       </c>
       <c r="J198" t="n">
-        <v>24.3371</v>
+        <v>22.9976</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.45</v>
       </c>
       <c r="I199" t="n">
-        <v>0.9403</v>
+        <v>1.0341</v>
       </c>
       <c r="J199" t="n">
-        <v>17.8657</v>
+        <v>19.6479</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.42</v>
       </c>
       <c r="I200" t="n">
-        <v>0.8744</v>
+        <v>0.989</v>
       </c>
       <c r="J200" t="n">
-        <v>16.6136</v>
+        <v>18.791</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.01</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1448</v>
+        <v>-0.059</v>
       </c>
       <c r="J201" t="n">
-        <v>-2.7512</v>
+        <v>-1.121</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.2</v>
       </c>
       <c r="I202" t="n">
-        <v>0.397</v>
+        <v>0.4517</v>
       </c>
       <c r="J202" t="n">
-        <v>11.91</v>
+        <v>13.551</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.14</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3073</v>
+        <v>0.3372</v>
       </c>
       <c r="J203" t="n">
-        <v>9.218999999999999</v>
+        <v>10.116</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.1</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2424</v>
+        <v>0.2567</v>
       </c>
       <c r="J204" t="n">
-        <v>7.272</v>
+        <v>7.701</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.71</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4997</v>
+        <v>-0.3223</v>
       </c>
       <c r="J205" t="n">
-        <v>-14.991</v>
+        <v>-9.669</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.66</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3696</v>
       </c>
       <c r="J206" t="n">
-        <v>-16.95</v>
+        <v>-11.088</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.37</v>
       </c>
       <c r="I207" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9689</v>
       </c>
       <c r="J207" t="n">
-        <v>29.472</v>
+        <v>29.067</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.35</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9386</v>
+        <v>0.9275</v>
       </c>
       <c r="J208" t="n">
-        <v>28.158</v>
+        <v>27.825</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.17</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4983</v>
+        <v>0.4973</v>
       </c>
       <c r="J209" t="n">
-        <v>14.949</v>
+        <v>14.919</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.01</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.0398</v>
+        <v>0.0216</v>
       </c>
       <c r="J210" t="n">
-        <v>-1.194</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7143</v>
+        <v>-0.6603</v>
       </c>
       <c r="J211" t="n">
-        <v>-21.429</v>
+        <v>-19.809</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.44</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1601</v>
+        <v>1.0946</v>
       </c>
       <c r="J212" t="n">
-        <v>41.7636</v>
+        <v>39.4056</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3651</v>
+        <v>0.3529</v>
       </c>
       <c r="J213" t="n">
-        <v>13.1436</v>
+        <v>12.7044</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.1</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3327</v>
+        <v>0.3255</v>
       </c>
       <c r="J214" t="n">
-        <v>11.9772</v>
+        <v>11.718</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.02</v>
       </c>
       <c r="I215" t="n">
-        <v>0.0331</v>
+        <v>0.0766</v>
       </c>
       <c r="J215" t="n">
-        <v>1.1916</v>
+        <v>2.7576</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.75</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.8161</v>
+        <v>-0.773</v>
       </c>
       <c r="J216" t="n">
-        <v>-29.3796</v>
+        <v>-27.828</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.05</v>
       </c>
       <c r="I217" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="J217" t="n">
-        <v>5.22</v>
+        <v>5.184</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.03</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1028</v>
+        <v>0.096</v>
       </c>
       <c r="J218" t="n">
-        <v>3.7008</v>
+        <v>3.456</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.03</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1028</v>
+        <v>0.096</v>
       </c>
       <c r="J219" t="n">
-        <v>3.7008</v>
+        <v>3.456</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0168</v>
+        <v>0.0029</v>
       </c>
       <c r="J220" t="n">
-        <v>0.6048</v>
+        <v>0.1044</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4071</v>
+        <v>-0.2563</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.6556</v>
+        <v>-9.226800000000001</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2.65</v>
       </c>
       <c r="I222" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J222" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.74</v>
       </c>
       <c r="I223" t="n">
-        <v>1.4802</v>
+        <v>1.3509</v>
       </c>
       <c r="J223" t="n">
-        <v>26.6436</v>
+        <v>24.3162</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.53</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0378</v>
+        <v>1.1164</v>
       </c>
       <c r="J224" t="n">
-        <v>18.6804</v>
+        <v>20.0952</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.3</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5708</v>
+        <v>0.7077</v>
       </c>
       <c r="J225" t="n">
-        <v>10.2744</v>
+        <v>12.7386</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.02</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.132</v>
+        <v>-0.0457</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.376</v>
+        <v>-0.8226</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.93</v>
       </c>
       <c r="I227" t="n">
-        <v>0.022</v>
+        <v>-0.0187</v>
       </c>
       <c r="J227" t="n">
-        <v>0.396</v>
+        <v>-0.3366</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.61</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.5122</v>
+        <v>-0.3669</v>
       </c>
       <c r="J228" t="n">
-        <v>-9.2196</v>
+        <v>-6.6042</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.5971</v>
+        <v>-0.412</v>
       </c>
       <c r="J229" t="n">
-        <v>-10.7478</v>
+        <v>-7.416</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.55</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.4212</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.0232</v>
+        <v>-7.5816</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.43</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7798</v>
+        <v>-0.5343</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.0364</v>
+        <v>-9.6174</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.36</v>
       </c>
       <c r="I232" t="n">
-        <v>0.632</v>
+        <v>0.7689</v>
       </c>
       <c r="J232" t="n">
-        <v>17.064</v>
+        <v>20.7603</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.16</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3608</v>
+        <v>0.3994</v>
       </c>
       <c r="J233" t="n">
-        <v>9.7416</v>
+        <v>10.7838</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.85</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2755</v>
+        <v>-0.1763</v>
       </c>
       <c r="J234" t="n">
-        <v>-7.4385</v>
+        <v>-4.7601</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.66</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5526</v>
+        <v>-0.362</v>
       </c>
       <c r="J235" t="n">
-        <v>-14.9202</v>
+        <v>-9.773999999999999</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.47</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7862</v>
+        <v>-0.5365</v>
       </c>
       <c r="J236" t="n">
-        <v>-21.2274</v>
+        <v>-14.4855</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.36</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9735</v>
+        <v>0.9575</v>
       </c>
       <c r="J237" t="n">
-        <v>26.2845</v>
+        <v>25.8525</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.31</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8622</v>
+        <v>0.8446</v>
       </c>
       <c r="J238" t="n">
-        <v>23.2794</v>
+        <v>22.8042</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.25</v>
       </c>
       <c r="I239" t="n">
-        <v>0.7216</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="J239" t="n">
-        <v>19.4832</v>
+        <v>18.9297</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.93</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3606</v>
+        <v>-0.292</v>
       </c>
       <c r="J240" t="n">
-        <v>-9.7362</v>
+        <v>-7.884</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8703</v>
+        <v>-0.8312</v>
       </c>
       <c r="J241" t="n">
-        <v>-23.4981</v>
+        <v>-22.4424</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.26</v>
       </c>
       <c r="I242" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J242" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.96</v>
       </c>
       <c r="I243" t="n">
-        <v>1.8951</v>
+        <v>1.6057</v>
       </c>
       <c r="J243" t="n">
-        <v>34.1118</v>
+        <v>28.9026</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.29</v>
       </c>
       <c r="I244" t="n">
-        <v>0.5709</v>
+        <v>0.7007</v>
       </c>
       <c r="J244" t="n">
-        <v>10.2762</v>
+        <v>12.6126</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.19</v>
       </c>
       <c r="I245" t="n">
-        <v>0.3468</v>
+        <v>0.4617</v>
       </c>
       <c r="J245" t="n">
-        <v>6.2424</v>
+        <v>8.310600000000001</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.12</v>
       </c>
       <c r="I246" t="n">
-        <v>0.1765</v>
+        <v>0.2792</v>
       </c>
       <c r="J246" t="n">
-        <v>3.177</v>
+        <v>5.0256</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.97</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0988</v>
+        <v>0.0684</v>
       </c>
       <c r="J247" t="n">
-        <v>1.7784</v>
+        <v>1.2312</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.89</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0508</v>
+        <v>-0.0725</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.9144</v>
+        <v>-1.305</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.51</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.6724</v>
+        <v>-0.4593</v>
       </c>
       <c r="J249" t="n">
-        <v>-12.1032</v>
+        <v>-8.2674</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.43</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.781</v>
+        <v>-0.535</v>
       </c>
       <c r="J250" t="n">
-        <v>-14.058</v>
+        <v>-9.630000000000001</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.3</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.9444</v>
+        <v>-0.659</v>
       </c>
       <c r="J251" t="n">
-        <v>-16.9992</v>
+        <v>-11.862</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.54</v>
       </c>
       <c r="I252" t="n">
-        <v>1.346</v>
+        <v>1.2181</v>
       </c>
       <c r="J252" t="n">
-        <v>34.996</v>
+        <v>31.6706</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.41</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0827</v>
+        <v>1.0453</v>
       </c>
       <c r="J253" t="n">
-        <v>28.1502</v>
+        <v>27.1778</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.09</v>
       </c>
       <c r="I254" t="n">
-        <v>0.2606</v>
+        <v>0.2937</v>
       </c>
       <c r="J254" t="n">
-        <v>6.7756</v>
+        <v>7.6362</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.8</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.7062</v>
+        <v>-0.653</v>
       </c>
       <c r="J255" t="n">
-        <v>-18.3612</v>
+        <v>-16.978</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.72</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8918</v>
+        <v>-0.8549</v>
       </c>
       <c r="J256" t="n">
-        <v>-23.1868</v>
+        <v>-22.2274</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5985</v>
+        <v>0.7217</v>
       </c>
       <c r="J257" t="n">
-        <v>15.561</v>
+        <v>18.7642</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.07</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1913</v>
+        <v>0.194</v>
       </c>
       <c r="J258" t="n">
-        <v>4.9738</v>
+        <v>5.044</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.91</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1949</v>
+        <v>-0.1186</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.0674</v>
+        <v>-3.0836</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.91</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1949</v>
+        <v>-0.1186</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.0674</v>
+        <v>-3.0836</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.55</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7</v>
+        <v>-0.4704</v>
       </c>
       <c r="J261" t="n">
-        <v>-18.2</v>
+        <v>-12.2304</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.17</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3982</v>
+        <v>0.4462</v>
       </c>
       <c r="J262" t="n">
-        <v>9.955</v>
+        <v>11.155</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.95</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0469</v>
+        <v>-0.0582</v>
       </c>
       <c r="J263" t="n">
-        <v>-1.1725</v>
+        <v>-1.455</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.74</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.426</v>
+        <v>-0.2781</v>
       </c>
       <c r="J264" t="n">
-        <v>-10.65</v>
+        <v>-6.9525</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.72</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4551</v>
+        <v>-0.2973</v>
       </c>
       <c r="J265" t="n">
-        <v>-11.3775</v>
+        <v>-7.4325</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.63</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5786</v>
+        <v>-0.3826</v>
       </c>
       <c r="J266" t="n">
-        <v>-14.465</v>
+        <v>-9.565</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.57</v>
       </c>
       <c r="I267" t="n">
-        <v>1.3197</v>
+        <v>1.21</v>
       </c>
       <c r="J267" t="n">
-        <v>32.9925</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.43</v>
       </c>
       <c r="I268" t="n">
-        <v>1.0363</v>
+        <v>1.0328</v>
       </c>
       <c r="J268" t="n">
-        <v>25.9075</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.21</v>
       </c>
       <c r="I269" t="n">
-        <v>0.4893</v>
+        <v>0.5693</v>
       </c>
       <c r="J269" t="n">
-        <v>12.2325</v>
+        <v>14.2325</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.11</v>
       </c>
       <c r="I270" t="n">
-        <v>0.2282</v>
+        <v>0.3109</v>
       </c>
       <c r="J270" t="n">
-        <v>5.705</v>
+        <v>7.7725</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.1</v>
       </c>
       <c r="I271" t="n">
-        <v>0.2005</v>
+        <v>0.2828</v>
       </c>
       <c r="J271" t="n">
-        <v>5.0125</v>
+        <v>7.07</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6018/event_6018_evp_summary.xlsx
+++ b/database/event/6018/event_6018_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.494300000000001</v>
+        <v>8.8414</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2012</v>
+        <v>1.2502</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1967</v>
+        <v>3.4006</v>
       </c>
       <c r="E2" t="n">
-        <v>8.494300000000001</v>
+        <v>8.8414</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0062</v>
+        <v>2.7649</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4881</v>
+        <v>6.0766</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2413</v>
+        <v>3.3265</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3746</v>
+        <v>3.4122</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4881</v>
+        <v>6.0766</v>
       </c>
       <c r="K2" t="n">
         <v>79</v>
@@ -529,7 +529,7 @@
         <v>244</v>
       </c>
       <c r="M2" t="n">
-        <v>8.8627</v>
+        <v>9.488799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>323</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.0726</v>
+        <v>7.3813</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0001</v>
+        <v>1.0438</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5549</v>
+        <v>2.7359</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0726</v>
+        <v>7.3813</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5806</v>
+        <v>1.581</v>
       </c>
       <c r="G3" t="n">
-        <v>5.492</v>
+        <v>5.8003</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5806</v>
+        <v>1.581</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6456</v>
+        <v>1.6217</v>
       </c>
       <c r="J3" t="n">
-        <v>5.492</v>
+        <v>5.8003</v>
       </c>
       <c r="K3" t="n">
         <v>79</v>
@@ -575,7 +575,7 @@
         <v>244</v>
       </c>
       <c r="M3" t="n">
-        <v>7.1376</v>
+        <v>7.422</v>
       </c>
       <c r="N3" t="n">
         <v>323</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2445</v>
+        <v>6.2745</v>
       </c>
       <c r="C4" t="n">
-        <v>0.883</v>
+        <v>0.8873</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1811</v>
+        <v>2.2321</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2445</v>
+        <v>6.2745</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8776</v>
+        <v>2.8446</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3669</v>
+        <v>3.4299</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6524</v>
+        <v>4.4914</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4191</v>
+        <v>2.4253</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3669</v>
+        <v>3.4299</v>
       </c>
       <c r="K4" t="n">
         <v>93</v>
@@ -621,7 +621,7 @@
         <v>175</v>
       </c>
       <c r="M4" t="n">
-        <v>5.786</v>
+        <v>5.8552</v>
       </c>
       <c r="N4" t="n">
         <v>268</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3235</v>
+        <v>5.6015</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7528</v>
+        <v>0.7921</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7653</v>
+        <v>1.9257</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3235</v>
+        <v>5.6015</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0016</v>
+        <v>0.0325</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3219</v>
+        <v>5.569</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0016</v>
+        <v>0.0325</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0017</v>
+        <v>0.0333</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3219</v>
+        <v>5.569</v>
       </c>
       <c r="K5" t="n">
         <v>79</v>
@@ -667,7 +667,7 @@
         <v>244</v>
       </c>
       <c r="M5" t="n">
-        <v>5.3236</v>
+        <v>5.6023</v>
       </c>
       <c r="N5" t="n">
         <v>323</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5999</v>
+        <v>3.7665</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5091</v>
+        <v>0.5326</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9872</v>
+        <v>1.0904</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5999</v>
+        <v>3.7665</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0796</v>
+        <v>3.16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5203</v>
+        <v>0.6065</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3644</v>
+        <v>5.532</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7892</v>
+        <v>2.9872</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5203</v>
+        <v>0.6065</v>
       </c>
       <c r="K6" t="n">
         <v>93</v>
@@ -713,7 +713,7 @@
         <v>175</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3095</v>
+        <v>3.5937</v>
       </c>
       <c r="N6" t="n">
         <v>268</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4446</v>
+        <v>3.5346</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4871</v>
+        <v>0.4998</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9171</v>
+        <v>0.9848</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4446</v>
+        <v>3.5346</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3095</v>
+        <v>2.2743</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1351</v>
+        <v>1.2603</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3095</v>
+        <v>2.2743</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4045</v>
+        <v>2.3329</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1351</v>
+        <v>1.2603</v>
       </c>
       <c r="K7" t="n">
         <v>76</v>
@@ -759,7 +759,7 @@
         <v>57</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5396</v>
+        <v>3.5932</v>
       </c>
       <c r="N7" t="n">
         <v>133</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Forester</t>
+          <t>h4rn</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.302</v>
+        <v>3.3593</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4669</v>
+        <v>0.475</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8527</v>
+        <v>0.905</v>
       </c>
       <c r="E8" t="n">
-        <v>3.302</v>
+        <v>3.3593</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8906</v>
+        <v>1.9336</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4114</v>
+        <v>1.4257</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6983</v>
+        <v>1.9336</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4429</v>
+        <v>1.9336</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4114</v>
+        <v>1.4257</v>
       </c>
       <c r="K8" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="L8" t="n">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8543</v>
+        <v>3.3593</v>
       </c>
       <c r="N8" t="n">
-        <v>268</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>h4rn</t>
+          <t>Forester</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2813</v>
+        <v>3.2266</v>
       </c>
       <c r="C9" t="n">
-        <v>0.464</v>
+        <v>0.4563</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8433</v>
+        <v>0.8446</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2813</v>
+        <v>3.2266</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9663</v>
+        <v>2.7793</v>
       </c>
       <c r="G9" t="n">
-        <v>1.315</v>
+        <v>0.4473</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9663</v>
+        <v>4.2758</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9663</v>
+        <v>2.3089</v>
       </c>
       <c r="J9" t="n">
-        <v>1.315</v>
+        <v>0.4473</v>
       </c>
       <c r="K9" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L9" t="n">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2813</v>
+        <v>2.7562</v>
       </c>
       <c r="N9" t="n">
-        <v>194</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1131</v>
+        <v>3.2022</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4402</v>
+        <v>0.4528</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7674</v>
+        <v>0.8335</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1131</v>
+        <v>3.2022</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6624</v>
+        <v>-0.4087</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4507</v>
+        <v>3.6109</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6624</v>
+        <v>-0.4087</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7719</v>
+        <v>-0.4192</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4507</v>
+        <v>3.6109</v>
       </c>
       <c r="K10" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L10" t="n">
-        <v>57</v>
+        <v>244</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2226</v>
+        <v>3.1917</v>
       </c>
       <c r="N10" t="n">
-        <v>133</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.044</v>
+        <v>3.1664</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4304</v>
+        <v>0.4478</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7362</v>
+        <v>0.8172</v>
       </c>
       <c r="E11" t="n">
-        <v>3.044</v>
+        <v>3.1664</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0312</v>
+        <v>0.9759</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0127</v>
+        <v>2.1905</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0312</v>
+        <v>0.9759</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5362</v>
+        <v>0.527</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0127</v>
+        <v>2.1905</v>
       </c>
       <c r="K11" t="n">
         <v>93</v>
@@ -943,7 +943,7 @@
         <v>175</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5489</v>
+        <v>2.7175</v>
       </c>
       <c r="N11" t="n">
         <v>268</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8099</v>
+        <v>2.9147</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3973</v>
+        <v>0.4122</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.7026</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8099</v>
+        <v>2.9147</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4302</v>
+        <v>2.4146</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2401</v>
+        <v>0.5001</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4302</v>
+        <v>2.5598</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4479</v>
+        <v>2.6258</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2401</v>
+        <v>0.5001</v>
       </c>
       <c r="K12" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L12" t="n">
-        <v>244</v>
+        <v>57</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7922</v>
+        <v>3.1259</v>
       </c>
       <c r="N12" t="n">
-        <v>323</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4328</v>
+        <v>2.4769</v>
       </c>
       <c r="C13" t="n">
-        <v>0.344</v>
+        <v>0.3503</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4603</v>
+        <v>0.5033</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4328</v>
+        <v>2.4769</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1353</v>
+        <v>3.092</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7025</v>
+        <v>-0.6151</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5607</v>
+        <v>5.3075</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8913</v>
+        <v>2.866</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7025</v>
+        <v>-0.6151</v>
       </c>
       <c r="K13" t="n">
         <v>93</v>
@@ -1035,7 +1035,7 @@
         <v>175</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1888</v>
+        <v>2.2509</v>
       </c>
       <c r="N13" t="n">
         <v>268</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3464</v>
+        <v>2.2668</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3318</v>
+        <v>0.3205</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4213</v>
+        <v>0.4077</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3464</v>
+        <v>2.2668</v>
       </c>
       <c r="F14" t="n">
-        <v>2.483</v>
+        <v>2.4148</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1366</v>
+        <v>-0.148</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2624</v>
+        <v>3.0732</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6963</v>
+        <v>1.6595</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1366</v>
+        <v>-0.148</v>
       </c>
       <c r="K14" t="n">
         <v>89</v>
@@ -1081,7 +1081,7 @@
         <v>49</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5597</v>
+        <v>1.5115</v>
       </c>
       <c r="N14" t="n">
         <v>138</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6376</v>
+        <v>1.4516</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2316</v>
+        <v>0.2053</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1013</v>
+        <v>0.0366</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6376</v>
+        <v>1.4516</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1885</v>
+        <v>2.0335</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.5819</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2244</v>
+        <v>2.0335</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1566</v>
+        <v>1.0981</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.5819</v>
       </c>
       <c r="K15" t="n">
         <v>89</v>
@@ -1127,7 +1127,7 @@
         <v>49</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6057000000000001</v>
+        <v>0.5162000000000001</v>
       </c>
       <c r="N15" t="n">
         <v>138</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4388</v>
+        <v>1.4024</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2035</v>
+        <v>0.1983</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0115</v>
+        <v>0.0142</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4388</v>
+        <v>1.4024</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8112</v>
+        <v>1.7727</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3724</v>
+        <v>-0.3703</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8112</v>
+        <v>1.7727</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8857</v>
+        <v>1.8184</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3724</v>
+        <v>-0.3703</v>
       </c>
       <c r="K16" t="n">
         <v>76</v>
@@ -1173,7 +1173,7 @@
         <v>57</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5133</v>
+        <v>1.4481</v>
       </c>
       <c r="N16" t="n">
         <v>133</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3516</v>
+        <v>1.3819</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1911</v>
+        <v>0.1954</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0278</v>
+        <v>0.0049</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3516</v>
+        <v>1.3819</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8603</v>
+        <v>0.8427</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4913</v>
+        <v>0.5392</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8603</v>
+        <v>0.8427</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4913</v>
+        <v>0.5392</v>
       </c>
       <c r="K17" t="n">
         <v>79</v>
@@ -1219,7 +1219,7 @@
         <v>244</v>
       </c>
       <c r="M17" t="n">
-        <v>1.387</v>
+        <v>1.4036</v>
       </c>
       <c r="N17" t="n">
         <v>323</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REDSTAR</t>
+          <t>mopoz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2118</v>
+        <v>1.2319</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1714</v>
+        <v>0.1742</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.0634</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2118</v>
+        <v>1.2319</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3923</v>
+        <v>0.8295</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1805</v>
+        <v>0.4024</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3923</v>
+        <v>0.8295</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3923</v>
+        <v>0.8509</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1805</v>
+        <v>0.4024</v>
       </c>
       <c r="K18" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="L18" t="n">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2118</v>
+        <v>1.2533</v>
       </c>
       <c r="N18" t="n">
-        <v>194</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mopoz</t>
+          <t>REDSTAR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2012</v>
+        <v>1.1683</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1699</v>
+        <v>0.1652</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0924</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2012</v>
+        <v>1.1683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8356</v>
+        <v>1.3385</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3656</v>
+        <v>-0.1702</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8356</v>
+        <v>1.3385</v>
       </c>
       <c r="I19" t="n">
-        <v>0.87</v>
+        <v>1.3385</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3656</v>
+        <v>-0.1702</v>
       </c>
       <c r="K19" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="L19" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2356</v>
+        <v>1.1683</v>
       </c>
       <c r="N19" t="n">
-        <v>133</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9469</v>
+        <v>0.9144</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1339</v>
+        <v>0.1293</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2105</v>
+        <v>-0.2079</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9469</v>
+        <v>0.9144</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5874</v>
+        <v>0.5092</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3595</v>
+        <v>0.4052</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5874</v>
+        <v>0.5092</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6116</v>
+        <v>0.5223</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3595</v>
+        <v>0.4052</v>
       </c>
       <c r="K20" t="n">
         <v>102</v>
@@ -1357,7 +1357,7 @@
         <v>69</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9711000000000001</v>
+        <v>0.9275</v>
       </c>
       <c r="N20" t="n">
         <v>171</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7778</v>
+        <v>0.7752</v>
       </c>
       <c r="C21" t="n">
-        <v>0.11</v>
+        <v>0.1096</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2869</v>
+        <v>-0.2713</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7778</v>
+        <v>0.7752</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4812</v>
+        <v>0.4864</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2966</v>
+        <v>0.2888</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4812</v>
+        <v>0.4864</v>
       </c>
       <c r="I21" t="n">
-        <v>0.501</v>
+        <v>0.4989</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2966</v>
+        <v>0.2888</v>
       </c>
       <c r="K21" t="n">
         <v>102</v>
@@ -1403,7 +1403,7 @@
         <v>69</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7976</v>
+        <v>0.7877000000000001</v>
       </c>
       <c r="N21" t="n">
         <v>171</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6882</v>
+        <v>0.72</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0973</v>
+        <v>0.1018</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3273</v>
+        <v>-0.2964</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6882</v>
+        <v>0.72</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3236</v>
+        <v>0.3414</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3646</v>
+        <v>0.3786</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3236</v>
+        <v>0.3414</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3236</v>
+        <v>0.3414</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3646</v>
+        <v>0.3786</v>
       </c>
       <c r="K22" t="n">
         <v>88</v>
@@ -1449,7 +1449,7 @@
         <v>106</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6881999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="N22" t="n">
         <v>194</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4576</v>
+        <v>0.351</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0496</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4314</v>
+        <v>-0.4644</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4576</v>
+        <v>0.351</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0051</v>
+        <v>0.9333</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5475</v>
+        <v>-0.5823</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0051</v>
+        <v>0.9333</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5226</v>
+        <v>0.504</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5475</v>
+        <v>-0.5823</v>
       </c>
       <c r="K23" t="n">
         <v>89</v>
@@ -1495,7 +1495,7 @@
         <v>49</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.02490000000000003</v>
+        <v>-0.07830000000000004</v>
       </c>
       <c r="N23" t="n">
         <v>138</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3034</v>
+        <v>0.2523</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0429</v>
+        <v>0.0357</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.501</v>
+        <v>-0.5094</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3034</v>
+        <v>0.2523</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3034</v>
+        <v>0.2523</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3034</v>
+        <v>0.2523</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3034</v>
+        <v>0.2523</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3034</v>
+        <v>0.2523</v>
       </c>
       <c r="N24" t="n">
         <v>80</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2566</v>
+        <v>0.1801</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0363</v>
+        <v>0.0255</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5222</v>
+        <v>-0.5422</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2566</v>
+        <v>0.1801</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2566</v>
+        <v>0.1801</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2566</v>
+        <v>0.1801</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2566</v>
+        <v>0.1801</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2566</v>
+        <v>0.1801</v>
       </c>
       <c r="N25" t="n">
         <v>67</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SHOCK</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0631</v>
+        <v>-0.0136</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0089</v>
+        <v>-0.0019</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6665</v>
+        <v>-0.6304</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0631</v>
+        <v>-0.0136</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0631</v>
+        <v>-0.1702</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.1566</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0631</v>
+        <v>-0.1702</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0631</v>
+        <v>-0.0919</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.1566</v>
       </c>
       <c r="K26" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0631</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>67</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.074</v>
+        <v>-0.0794</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0105</v>
+        <v>-0.0112</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6714</v>
+        <v>-0.6603</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.074</v>
+        <v>-0.0794</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.074</v>
+        <v>-0.0794</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.074</v>
+        <v>-0.0794</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.074</v>
+        <v>-0.0794</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.074</v>
+        <v>-0.0794</v>
       </c>
       <c r="N27" t="n">
         <v>80</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>SHOCK</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1595</v>
+        <v>-0.0927</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0226</v>
+        <v>-0.0131</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.71</v>
+        <v>-0.6664</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1595</v>
+        <v>-0.0927</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2829</v>
+        <v>-0.0927</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1234</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2829</v>
+        <v>-0.0927</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1471</v>
+        <v>-0.0927</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1234</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L28" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.02370000000000001</v>
+        <v>-0.0927</v>
       </c>
       <c r="N28" t="n">
-        <v>138</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2424</v>
+        <v>-0.3423</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0343</v>
+        <v>-0.0484</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7474</v>
+        <v>-0.78</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2424</v>
+        <v>-0.3423</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2553</v>
+        <v>0.201</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4977</v>
+        <v>-0.5433</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2553</v>
+        <v>0.201</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2658</v>
+        <v>0.2062</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4977</v>
+        <v>-0.5433</v>
       </c>
       <c r="K29" t="n">
         <v>102</v>
@@ -1771,7 +1771,7 @@
         <v>69</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2319</v>
+        <v>-0.3371</v>
       </c>
       <c r="N29" t="n">
         <v>171</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3936</v>
+        <v>-0.4501</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0557</v>
+        <v>-0.0636</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8157</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3936</v>
+        <v>-0.4501</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.3936</v>
+        <v>-0.4501</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3936</v>
+        <v>-0.4501</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3936</v>
+        <v>-0.4501</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3936</v>
+        <v>-0.4501</v>
       </c>
       <c r="N30" t="n">
         <v>80</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3991</v>
+        <v>-0.4649</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0564</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8182</v>
+        <v>-0.8358</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3991</v>
+        <v>-0.4649</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6009</v>
+        <v>0.5351</v>
       </c>
       <c r="G31" t="n">
         <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6009</v>
+        <v>0.5351</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6256</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>69</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3744</v>
+        <v>-0.4510999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>171</v>
@@ -1872,139 +1872,139 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.476</v>
+        <v>-0.4915</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0673</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8529</v>
+        <v>-0.8479</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.476</v>
+        <v>-0.4915</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.476</v>
+        <v>-0.4076</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.0839</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.476</v>
+        <v>-0.4076</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.476</v>
+        <v>-0.2201</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.0839</v>
       </c>
       <c r="K32" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.476</v>
+        <v>-0.304</v>
       </c>
       <c r="N32" t="n">
-        <v>67</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>luko</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5569</v>
+        <v>-0.5123</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0788</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8894</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5569</v>
+        <v>-0.5123</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5569</v>
+        <v>-0.5123</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5569</v>
+        <v>-0.5123</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5569</v>
+        <v>-0.5123</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5569</v>
+        <v>-0.5123</v>
       </c>
       <c r="N33" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>luko</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6044</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.081</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9109</v>
+        <v>-0.8851</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6044</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5345</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0699</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5345</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2779</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.0699</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L34" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3478</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>138</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7413</v>
+        <v>-0.761</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1048</v>
+        <v>-0.1076</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9727</v>
+        <v>-0.9706</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7413</v>
+        <v>-0.761</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7413</v>
+        <v>-0.761</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7413</v>
+        <v>-0.761</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7413</v>
+        <v>-0.761</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7413</v>
+        <v>-0.761</v>
       </c>
       <c r="N35" t="n">
         <v>80</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9292</v>
+        <v>-0.9811</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1314</v>
+        <v>-0.1387</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0575</v>
+        <v>-1.0708</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9292</v>
+        <v>-0.9811</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9292</v>
+        <v>-0.9811</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9292</v>
+        <v>-0.9811</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9292</v>
+        <v>-0.9811</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9292</v>
+        <v>-0.9811</v>
       </c>
       <c r="N36" t="n">
         <v>67</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0236</v>
+        <v>-1.0177</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1447</v>
+        <v>-0.1439</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1001</v>
+        <v>-1.0875</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0236</v>
+        <v>-1.0177</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6025</v>
+        <v>0.6079</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.6261</v>
+        <v>-1.6256</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6025</v>
+        <v>0.6079</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6025</v>
+        <v>0.6079</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.6261</v>
+        <v>-1.6256</v>
       </c>
       <c r="K37" t="n">
         <v>88</v>
@@ -2139,7 +2139,7 @@
         <v>106</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0236</v>
+        <v>-1.0177</v>
       </c>
       <c r="N37" t="n">
         <v>194</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1968</v>
+        <v>-1.2213</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1692</v>
+        <v>-0.1727</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1783</v>
+        <v>-1.1802</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1968</v>
+        <v>-1.2213</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0603</v>
+        <v>0.0305</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.2571</v>
+        <v>-1.2518</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0603</v>
+        <v>0.0305</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0603</v>
+        <v>0.0305</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.2571</v>
+        <v>-1.2518</v>
       </c>
       <c r="K38" t="n">
         <v>88</v>
@@ -2185,7 +2185,7 @@
         <v>106</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1968</v>
+        <v>-1.2213</v>
       </c>
       <c r="N38" t="n">
         <v>194</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3914</v>
+        <v>-1.4224</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1968</v>
+        <v>-0.2011</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2662</v>
+        <v>-1.2717</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3914</v>
+        <v>-1.4224</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3914</v>
+        <v>-1.4224</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3914</v>
+        <v>-1.4224</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3914</v>
+        <v>-1.4224</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3914</v>
+        <v>-1.4224</v>
       </c>
       <c r="N39" t="n">
         <v>67</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6666</v>
+        <v>-1.6654</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2357</v>
+        <v>-0.2355</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3904</v>
+        <v>-1.3823</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6666</v>
+        <v>-1.6654</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5515</v>
+        <v>-1.541</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1151</v>
+        <v>-0.1244</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5515</v>
+        <v>-1.541</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6153</v>
+        <v>-1.5807</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1151</v>
+        <v>-0.1244</v>
       </c>
       <c r="K40" t="n">
         <v>102</v>
@@ -2277,7 +2277,7 @@
         <v>69</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7304</v>
+        <v>-1.7051</v>
       </c>
       <c r="N40" t="n">
         <v>171</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8083</v>
+        <v>-1.7677</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2557</v>
+        <v>-0.25</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4544</v>
+        <v>-1.4289</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8083</v>
+        <v>-1.7677</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2062</v>
+        <v>-1.1455</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6021</v>
+        <v>-0.6222</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2062</v>
+        <v>-1.1455</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2558</v>
+        <v>-1.175</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6021</v>
+        <v>-0.6222</v>
       </c>
       <c r="K41" t="n">
         <v>76</v>
@@ -2323,7 +2323,7 @@
         <v>57</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8579</v>
+        <v>-1.7972</v>
       </c>
       <c r="N41" t="n">
         <v>133</v>
@@ -2429,10 +2429,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0331</v>
+        <v>0.989</v>
       </c>
       <c r="J2" t="n">
-        <v>26.8606</v>
+        <v>25.714</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.32</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8193</v>
+        <v>0.7794</v>
       </c>
       <c r="J3" t="n">
-        <v>21.3018</v>
+        <v>20.2644</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.28</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7316</v>
+        <v>0.7016</v>
       </c>
       <c r="J4" t="n">
-        <v>19.0216</v>
+        <v>18.2416</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.22</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5938</v>
+        <v>0.5785</v>
       </c>
       <c r="J5" t="n">
-        <v>15.4388</v>
+        <v>15.041</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.445</v>
+        <v>0.4446</v>
       </c>
       <c r="J6" t="n">
-        <v>11.57</v>
+        <v>11.5596</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0313</v>
+        <v>0.0226</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8138</v>
+        <v>0.5876</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.1137</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.5636</v>
+        <v>-2.9562</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.85</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1728</v>
+        <v>-0.1898</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.4928</v>
+        <v>-4.9348</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.78</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2423</v>
+        <v>-0.2592</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.2998</v>
+        <v>-6.7392</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.78</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2423</v>
+        <v>-0.2592</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.2998</v>
+        <v>-6.7392</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.56</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1993</v>
+        <v>1.228</v>
       </c>
       <c r="J12" t="n">
-        <v>33.5804</v>
+        <v>34.384</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9868</v>
+        <v>0.9338</v>
       </c>
       <c r="J13" t="n">
-        <v>27.6304</v>
+        <v>26.1464</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.38</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9495</v>
+        <v>0.8958</v>
       </c>
       <c r="J14" t="n">
-        <v>26.586</v>
+        <v>25.0824</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6187</v>
+        <v>0.6006</v>
       </c>
       <c r="J15" t="n">
-        <v>17.3236</v>
+        <v>16.8168</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6665</v>
+        <v>-0.6145</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.662</v>
+        <v>-17.206</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.464</v>
+        <v>0.4452</v>
       </c>
       <c r="J17" t="n">
-        <v>12.992</v>
+        <v>12.4656</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3209</v>
+        <v>0.3116</v>
       </c>
       <c r="J18" t="n">
-        <v>8.985200000000001</v>
+        <v>8.7248</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.88</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1405</v>
+        <v>-0.1573</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.934</v>
+        <v>-4.4044</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.71</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3074</v>
+        <v>-0.3233</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.607200000000001</v>
+        <v>-9.0524</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.35</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6387</v>
+        <v>-0.6368</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.8836</v>
+        <v>-17.8304</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3376</v>
+        <v>0.3383</v>
       </c>
       <c r="J22" t="n">
-        <v>9.7904</v>
+        <v>9.810700000000001</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.08</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1691</v>
+        <v>0.1755</v>
       </c>
       <c r="J23" t="n">
-        <v>4.9039</v>
+        <v>5.0895</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1278</v>
+        <v>-0.1419</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.7062</v>
+        <v>-4.1151</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.77</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2616</v>
+        <v>-0.2761</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.5864</v>
+        <v>-8.0069</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.76</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2714</v>
+        <v>-0.2858</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.8706</v>
+        <v>-8.2882</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.57</v>
       </c>
       <c r="I27" t="n">
-        <v>0.714</v>
+        <v>0.7068</v>
       </c>
       <c r="J27" t="n">
-        <v>20.706</v>
+        <v>20.4972</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4081</v>
+        <v>0.4199</v>
       </c>
       <c r="J28" t="n">
-        <v>11.8349</v>
+        <v>12.1771</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.13</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1993</v>
+        <v>0.216</v>
       </c>
       <c r="J29" t="n">
-        <v>5.7797</v>
+        <v>6.264</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1495</v>
+        <v>-0.1588</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.3355</v>
+        <v>-4.6052</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2443</v>
+        <v>-0.2545</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.0847</v>
+        <v>-7.3805</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0469</v>
+        <v>0.0349</v>
       </c>
       <c r="J32" t="n">
-        <v>1.0787</v>
+        <v>0.8027</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.91</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0977</v>
+        <v>-0.1159</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.2471</v>
+        <v>-2.6657</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.84</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1749</v>
+        <v>-0.1939</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.0227</v>
+        <v>-4.4597</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2148</v>
+        <v>-0.2337</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.9404</v>
+        <v>-5.3751</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5877</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.5171</v>
+        <v>-13.5746</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.76</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8727</v>
+        <v>0.859</v>
       </c>
       <c r="J37" t="n">
-        <v>20.0721</v>
+        <v>19.757</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.4</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4964</v>
+        <v>0.5088</v>
       </c>
       <c r="J38" t="n">
-        <v>11.4172</v>
+        <v>11.7024</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.28</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3657</v>
+        <v>0.3833</v>
       </c>
       <c r="J39" t="n">
-        <v>8.411099999999999</v>
+        <v>8.815899999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.16</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2204</v>
+        <v>0.2414</v>
       </c>
       <c r="J40" t="n">
-        <v>5.0692</v>
+        <v>5.5522</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.96</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0963</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.1574</v>
+        <v>-2.2149</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.05</v>
       </c>
       <c r="I42" t="n">
-        <v>1.6973</v>
+        <v>1.8453</v>
       </c>
       <c r="J42" t="n">
-        <v>33.946</v>
+        <v>36.906</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>2.05</v>
       </c>
       <c r="I43" t="n">
-        <v>1.6973</v>
+        <v>1.8453</v>
       </c>
       <c r="J43" t="n">
-        <v>33.946</v>
+        <v>36.906</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.43</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9908</v>
+        <v>0.949</v>
       </c>
       <c r="J44" t="n">
-        <v>19.816</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.24</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5773</v>
+        <v>0.5764</v>
       </c>
       <c r="J45" t="n">
-        <v>11.546</v>
+        <v>11.528</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.22</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5291</v>
+        <v>0.5335</v>
       </c>
       <c r="J46" t="n">
-        <v>10.582</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.07</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5977</v>
+        <v>0.4995</v>
       </c>
       <c r="J47" t="n">
-        <v>11.954</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.4</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.5325</v>
+        <v>-0.5467</v>
       </c>
       <c r="J48" t="n">
-        <v>-10.65</v>
+        <v>-10.934</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.36</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5719</v>
+        <v>-0.5828</v>
       </c>
       <c r="J49" t="n">
-        <v>-11.438</v>
+        <v>-11.656</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.33</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6019</v>
+        <v>-0.6102</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.038</v>
+        <v>-12.204</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.2</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7353</v>
+        <v>-0.7308</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.706</v>
+        <v>-14.616</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.57</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9663</v>
+        <v>1.0606</v>
       </c>
       <c r="J52" t="n">
-        <v>27.0564</v>
+        <v>29.6968</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.35</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6786</v>
+        <v>0.7508</v>
       </c>
       <c r="J53" t="n">
-        <v>19.0008</v>
+        <v>21.0224</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2231</v>
+        <v>0.2344</v>
       </c>
       <c r="J54" t="n">
-        <v>6.2468</v>
+        <v>6.5632</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.93</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3053</v>
+        <v>-0.291</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.548400000000001</v>
+        <v>-8.148</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.91</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3656</v>
+        <v>-0.3471</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.2368</v>
+        <v>-9.7188</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.12</v>
       </c>
       <c r="I57" t="n">
-        <v>0.311</v>
+        <v>0.3091</v>
       </c>
       <c r="J57" t="n">
-        <v>8.708</v>
+        <v>8.6548</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0814</v>
+        <v>-0.0939</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.2792</v>
+        <v>-2.6292</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.115</v>
+        <v>-0.1292</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.22</v>
+        <v>-3.6176</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.89</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1366</v>
+        <v>-0.1515</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.8248</v>
+        <v>-4.242</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2883</v>
+        <v>-0.3029</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.0724</v>
+        <v>-8.481199999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.62</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9655</v>
+        <v>1.0713</v>
       </c>
       <c r="J62" t="n">
-        <v>20.2755</v>
+        <v>22.4973</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.6</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.0461</v>
       </c>
       <c r="J63" t="n">
-        <v>19.782</v>
+        <v>21.9681</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.56</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8949</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>18.7929</v>
+        <v>20.9055</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.32</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6028</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>12.6588</v>
+        <v>14.1939</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3925</v>
+        <v>0.4385</v>
       </c>
       <c r="J66" t="n">
-        <v>8.2425</v>
+        <v>9.208500000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.84</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1529</v>
+        <v>-0.1768</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.2109</v>
+        <v>-3.7128</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.82</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.175</v>
+        <v>-0.1985</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.675</v>
+        <v>-4.1685</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.65</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3403</v>
+        <v>-0.3596</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.1463</v>
+        <v>-7.5516</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.368</v>
+        <v>-0.3861</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.728</v>
+        <v>-8.1081</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.49</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4895</v>
+        <v>-0.5007</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.2795</v>
+        <v>-10.5147</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.8</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1919</v>
+        <v>-0.216</v>
       </c>
       <c r="J72" t="n">
-        <v>-4.0299</v>
+        <v>-4.536</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.72</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2739</v>
+        <v>-0.2957</v>
       </c>
       <c r="J73" t="n">
-        <v>-5.7519</v>
+        <v>-6.2097</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.63</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.356</v>
+        <v>-0.3751</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.476</v>
+        <v>-7.8771</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.6</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3836</v>
+        <v>-0.4014</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.0556</v>
+        <v>-8.429399999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4022</v>
+        <v>-0.4191</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.446199999999999</v>
+        <v>-8.8011</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.22</v>
       </c>
       <c r="I77" t="n">
-        <v>1.6485</v>
+        <v>1.7879</v>
       </c>
       <c r="J77" t="n">
-        <v>34.6185</v>
+        <v>37.5459</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.67</v>
       </c>
       <c r="I78" t="n">
-        <v>1.0265</v>
+        <v>1.1361</v>
       </c>
       <c r="J78" t="n">
-        <v>21.5565</v>
+        <v>23.8581</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.32</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6047</v>
+        <v>0.6775</v>
       </c>
       <c r="J79" t="n">
-        <v>12.6987</v>
+        <v>14.2275</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.22</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4678</v>
+        <v>0.5253</v>
       </c>
       <c r="J80" t="n">
-        <v>9.8238</v>
+        <v>11.0313</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8242</v>
+        <v>-0.7489</v>
       </c>
       <c r="J81" t="n">
-        <v>-17.3082</v>
+        <v>-15.7269</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.28</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4794</v>
+        <v>0.5317</v>
       </c>
       <c r="J82" t="n">
-        <v>13.4232</v>
+        <v>14.8876</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2656</v>
+        <v>0.2711</v>
       </c>
       <c r="J83" t="n">
-        <v>7.4368</v>
+        <v>7.5908</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.08</v>
       </c>
       <c r="I84" t="n">
-        <v>0.204</v>
+        <v>0.2118</v>
       </c>
       <c r="J84" t="n">
-        <v>5.712</v>
+        <v>5.9304</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1673</v>
+        <v>-0.1805</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.6844</v>
+        <v>-5.054</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.68</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3556</v>
+        <v>-0.3663</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.956799999999999</v>
+        <v>-10.2564</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.58</v>
       </c>
       <c r="I87" t="n">
-        <v>0.976</v>
+        <v>1.0715</v>
       </c>
       <c r="J87" t="n">
-        <v>27.328</v>
+        <v>30.002</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.46</v>
       </c>
       <c r="I88" t="n">
-        <v>0.822</v>
+        <v>0.9066</v>
       </c>
       <c r="J88" t="n">
-        <v>23.016</v>
+        <v>25.3848</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.28</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5814</v>
+        <v>0.6443</v>
       </c>
       <c r="J89" t="n">
-        <v>16.2792</v>
+        <v>18.0404</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.97</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1759</v>
+        <v>-0.1672</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.9252</v>
+        <v>-4.6816</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.1799</v>
+        <v>-1.0666</v>
       </c>
       <c r="J91" t="n">
-        <v>-33.0372</v>
+        <v>-29.8648</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.3</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4859</v>
+        <v>0.5422</v>
       </c>
       <c r="J92" t="n">
-        <v>13.6052</v>
+        <v>15.1816</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4148</v>
+        <v>0.4599</v>
       </c>
       <c r="J93" t="n">
-        <v>11.6144</v>
+        <v>12.8772</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.22</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4044</v>
+        <v>0.4468</v>
       </c>
       <c r="J94" t="n">
-        <v>11.3232</v>
+        <v>12.5104</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0558</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="J95" t="n">
-        <v>1.5624</v>
+        <v>1.8508</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4364</v>
+        <v>-0.4429</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.2192</v>
+        <v>-12.4012</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.24</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5504</v>
+        <v>0.604</v>
       </c>
       <c r="J97" t="n">
-        <v>15.4112</v>
+        <v>16.912</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4142</v>
+        <v>0.4505</v>
       </c>
       <c r="J98" t="n">
-        <v>11.5976</v>
+        <v>12.614</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.11</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3499</v>
+        <v>0.3571</v>
       </c>
       <c r="J99" t="n">
-        <v>9.7972</v>
+        <v>9.998799999999999</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.96</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1774</v>
+        <v>-0.1777</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.9672</v>
+        <v>-4.9756</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.79</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.6207</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.5304</v>
+        <v>-17.3796</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7307</v>
+        <v>0.8135</v>
       </c>
       <c r="J102" t="n">
-        <v>21.1903</v>
+        <v>23.5915</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.98</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0352</v>
+        <v>-0.0421</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.0208</v>
+        <v>-1.2209</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.97</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0492</v>
+        <v>-0.0575</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.4268</v>
+        <v>-1.6675</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.87</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1657</v>
+        <v>-0.1793</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.8053</v>
+        <v>-5.1997</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.6</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4282</v>
+        <v>-0.4364</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.4178</v>
+        <v>-12.6556</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.43</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8216</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>23.8264</v>
+        <v>26.0623</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.19</v>
       </c>
       <c r="I108" t="n">
-        <v>0.478</v>
+        <v>0.5229</v>
       </c>
       <c r="J108" t="n">
-        <v>13.862</v>
+        <v>15.1641</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.97</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.14</v>
+        <v>-0.1423</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.06</v>
+        <v>-4.1267</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.9</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3604</v>
+        <v>-0.35</v>
       </c>
       <c r="J110" t="n">
-        <v>-10.4516</v>
+        <v>-10.15</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.71</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.8605</v>
+        <v>-0.7957</v>
       </c>
       <c r="J111" t="n">
-        <v>-24.9545</v>
+        <v>-23.0753</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4899</v>
+        <v>0.544</v>
       </c>
       <c r="J112" t="n">
-        <v>13.7172</v>
+        <v>15.232</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1524</v>
+        <v>0.1589</v>
       </c>
       <c r="J113" t="n">
-        <v>4.2672</v>
+        <v>4.4492</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.8</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2318</v>
+        <v>-0.2468</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.4904</v>
+        <v>-6.9104</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.78</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2517</v>
+        <v>-0.2665</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.0476</v>
+        <v>-7.462</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.67</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3576</v>
+        <v>-0.3696</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.0128</v>
+        <v>-10.3488</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.63</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.6755</v>
       </c>
       <c r="J117" t="n">
-        <v>16.5256</v>
+        <v>18.914</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.29</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3672</v>
+        <v>0.4039</v>
       </c>
       <c r="J118" t="n">
-        <v>10.2816</v>
+        <v>11.3092</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.27</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3533</v>
+        <v>0.3815</v>
       </c>
       <c r="J119" t="n">
-        <v>9.8924</v>
+        <v>10.682</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.87</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.186</v>
+        <v>-0.1952</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.208</v>
+        <v>-5.4656</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2175</v>
+        <v>-0.2269</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.09</v>
+        <v>-6.3532</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.54</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8789</v>
+        <v>0.9766</v>
       </c>
       <c r="J122" t="n">
-        <v>16.6991</v>
+        <v>18.5554</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.49</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8185</v>
+        <v>0.9113</v>
       </c>
       <c r="J123" t="n">
-        <v>15.5515</v>
+        <v>17.3147</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.48</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8064</v>
+        <v>0.8982</v>
       </c>
       <c r="J124" t="n">
-        <v>15.3216</v>
+        <v>17.0658</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.32</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6092</v>
+        <v>0.6815</v>
       </c>
       <c r="J125" t="n">
-        <v>11.5748</v>
+        <v>12.9485</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.16</v>
       </c>
       <c r="I126" t="n">
-        <v>0.3843</v>
+        <v>0.4253</v>
       </c>
       <c r="J126" t="n">
-        <v>7.3017</v>
+        <v>8.0807</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0983</v>
+        <v>0.0718</v>
       </c>
       <c r="J127" t="n">
-        <v>1.8677</v>
+        <v>1.3642</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.9</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0934</v>
+        <v>-0.1154</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.7746</v>
+        <v>-2.1926</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.76</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2444</v>
+        <v>-0.265</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.6436</v>
+        <v>-5.035</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.7</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2995</v>
+        <v>-0.319</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.6905</v>
+        <v>-6.061</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.24</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7268</v>
+        <v>-0.7195</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.8092</v>
+        <v>-13.6705</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.01</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4643</v>
+        <v>1.5894</v>
       </c>
       <c r="J132" t="n">
-        <v>32.2146</v>
+        <v>34.9668</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.25</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5291</v>
+        <v>0.5891</v>
       </c>
       <c r="J133" t="n">
-        <v>11.6402</v>
+        <v>12.9602</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1658</v>
+        <v>0.1869</v>
       </c>
       <c r="J134" t="n">
-        <v>3.6476</v>
+        <v>4.1118</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1658</v>
+        <v>0.1869</v>
       </c>
       <c r="J135" t="n">
-        <v>3.6476</v>
+        <v>4.1118</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0672</v>
+        <v>-0.0466</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.4784</v>
+        <v>-1.0252</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.0673</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J137" t="n">
-        <v>-1.4806</v>
+        <v>-1.8282</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.88</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1373</v>
+        <v>-0.1549</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.0206</v>
+        <v>-3.4078</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1689</v>
+        <v>-0.1869</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.7158</v>
+        <v>-4.1118</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1689</v>
+        <v>-0.1869</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.7158</v>
+        <v>-4.1118</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.59</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4171</v>
+        <v>-0.4292</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.1762</v>
+        <v>-9.442399999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.37</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.8939</v>
       </c>
       <c r="J142" t="n">
-        <v>28.563</v>
+        <v>26.817</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.27</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7262</v>
+        <v>0.6932</v>
       </c>
       <c r="J143" t="n">
-        <v>21.786</v>
+        <v>20.796</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.25</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6793</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>20.379</v>
+        <v>19.551</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.18</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5137</v>
+        <v>0.5028</v>
       </c>
       <c r="J145" t="n">
-        <v>15.411</v>
+        <v>15.084</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4302</v>
+        <v>-0.4051</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.906</v>
+        <v>-12.153</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.11</v>
       </c>
       <c r="I147" t="n">
-        <v>0.312</v>
+        <v>0.3051</v>
       </c>
       <c r="J147" t="n">
-        <v>9.359999999999999</v>
+        <v>9.153</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1008</v>
+        <v>0.0985</v>
       </c>
       <c r="J148" t="n">
-        <v>3.024</v>
+        <v>2.955</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.84</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1828</v>
+        <v>-0.1999</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.484</v>
+        <v>-5.997</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.71</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3101</v>
+        <v>-0.3254</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.303000000000001</v>
+        <v>-9.762</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.367</v>
+        <v>-0.3803</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.01</v>
+        <v>-11.409</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0091</v>
+        <v>-0.0165</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.2275</v>
+        <v>-0.4125</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0785</v>
+        <v>-0.0917</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.9625</v>
+        <v>-2.2925</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.91</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1132</v>
+        <v>-0.1279</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.83</v>
+        <v>-3.1975</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.82</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2061</v>
+        <v>-0.2225</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.1525</v>
+        <v>-5.5625</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2161</v>
+        <v>-0.2325</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.4025</v>
+        <v>-5.8125</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4652</v>
+        <v>0.4724</v>
       </c>
       <c r="J157" t="n">
-        <v>11.63</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2561</v>
+        <v>0.2712</v>
       </c>
       <c r="J158" t="n">
-        <v>6.4025</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0375</v>
+        <v>0.0475</v>
       </c>
       <c r="J159" t="n">
-        <v>0.9375</v>
+        <v>1.1875</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.97</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0592</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.48</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.96</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0726</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J161" t="n">
-        <v>-1.815</v>
+        <v>-1.9925</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>2.03</v>
       </c>
       <c r="I162" t="n">
-        <v>1.7125</v>
+        <v>1.7174</v>
       </c>
       <c r="J162" t="n">
-        <v>34.25</v>
+        <v>34.348</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.37</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9033</v>
+        <v>0.8583</v>
       </c>
       <c r="J163" t="n">
-        <v>18.066</v>
+        <v>17.166</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.37</v>
       </c>
       <c r="I164" t="n">
-        <v>0.9033</v>
+        <v>0.8583</v>
       </c>
       <c r="J164" t="n">
-        <v>18.066</v>
+        <v>17.166</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.21</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5375</v>
+        <v>0.5346</v>
       </c>
       <c r="J165" t="n">
-        <v>10.75</v>
+        <v>10.692</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.19</v>
       </c>
       <c r="I166" t="n">
-        <v>0.4879</v>
+        <v>0.4902</v>
       </c>
       <c r="J166" t="n">
-        <v>9.757999999999999</v>
+        <v>9.804</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.04</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2249</v>
+        <v>0.2044</v>
       </c>
       <c r="J167" t="n">
-        <v>4.498</v>
+        <v>4.088</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.89</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1058</v>
+        <v>-0.1277</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.116</v>
+        <v>-2.554</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.62</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3741</v>
+        <v>-0.3908</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.482</v>
+        <v>-7.816</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.62</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3741</v>
+        <v>-0.3908</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.482</v>
+        <v>-7.816</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.44</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5421</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.842</v>
+        <v>-10.978</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.17</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3835</v>
+        <v>0.3822</v>
       </c>
       <c r="J172" t="n">
-        <v>13.806</v>
+        <v>13.7592</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3455</v>
+        <v>0.3466</v>
       </c>
       <c r="J173" t="n">
-        <v>12.438</v>
+        <v>12.4776</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.08</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2054</v>
+        <v>0.2127</v>
       </c>
       <c r="J174" t="n">
-        <v>7.3944</v>
+        <v>7.6572</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.99</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0204</v>
+        <v>-0.0251</v>
       </c>
       <c r="J175" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.9036</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.429</v>
+        <v>-0.437</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.444</v>
+        <v>-15.732</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.32</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9085</v>
+        <v>0.8418</v>
       </c>
       <c r="J177" t="n">
-        <v>32.706</v>
+        <v>30.3048</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5316</v>
+        <v>0.5097</v>
       </c>
       <c r="J178" t="n">
-        <v>19.1376</v>
+        <v>18.3492</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.01</v>
       </c>
       <c r="I179" t="n">
-        <v>0.0493</v>
+        <v>0.056</v>
       </c>
       <c r="J179" t="n">
-        <v>1.7748</v>
+        <v>2.016</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4962</v>
+        <v>-0.4743</v>
       </c>
       <c r="J180" t="n">
-        <v>-17.8632</v>
+        <v>-17.0748</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.78</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6806</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="J181" t="n">
-        <v>-24.5016</v>
+        <v>-22.9896</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.27</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5395</v>
       </c>
       <c r="J182" t="n">
-        <v>14.8743</v>
+        <v>14.5665</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.02</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0612</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>1.6524</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.99</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.024</v>
+        <v>-0.0278</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.648</v>
+        <v>-0.7506</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.97</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0539</v>
+        <v>-0.0611</v>
       </c>
       <c r="J185" t="n">
-        <v>-1.4553</v>
+        <v>-1.6497</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.95</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.08</v>
+        <v>-0.0892</v>
       </c>
       <c r="J186" t="n">
-        <v>-2.16</v>
+        <v>-2.4084</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.21</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6075</v>
+        <v>0.5828</v>
       </c>
       <c r="J187" t="n">
-        <v>16.4025</v>
+        <v>15.7356</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4289</v>
+        <v>0.422</v>
       </c>
       <c r="J188" t="n">
-        <v>11.5803</v>
+        <v>11.394</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.08</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2671</v>
+        <v>0.272</v>
       </c>
       <c r="J189" t="n">
-        <v>7.2117</v>
+        <v>7.344</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.05</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1762</v>
+        <v>0.186</v>
       </c>
       <c r="J190" t="n">
-        <v>4.7574</v>
+        <v>5.022</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.03</v>
       </c>
       <c r="I191" t="n">
-        <v>0.109</v>
+        <v>0.1212</v>
       </c>
       <c r="J191" t="n">
-        <v>2.943</v>
+        <v>3.2724</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.07</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3392</v>
+        <v>0.3062</v>
       </c>
       <c r="J192" t="n">
-        <v>6.4448</v>
+        <v>5.8178</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.84</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.149</v>
+        <v>-0.1738</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.831</v>
+        <v>-3.3022</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.51</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4684</v>
+        <v>-0.4813</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.8996</v>
+        <v>-9.1447</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.49</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4871</v>
+        <v>-0.4989</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.254899999999999</v>
+        <v>-9.479100000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.44</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5341</v>
+        <v>-0.5427</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.1479</v>
+        <v>-10.3113</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.99</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6533</v>
+        <v>1.6579</v>
       </c>
       <c r="J197" t="n">
-        <v>31.4127</v>
+        <v>31.5001</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.6</v>
       </c>
       <c r="I198" t="n">
-        <v>1.2104</v>
+        <v>1.1888</v>
       </c>
       <c r="J198" t="n">
-        <v>22.9976</v>
+        <v>22.5872</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.45</v>
       </c>
       <c r="I199" t="n">
-        <v>1.0341</v>
+        <v>0.992</v>
       </c>
       <c r="J199" t="n">
-        <v>19.6479</v>
+        <v>18.848</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.42</v>
       </c>
       <c r="I200" t="n">
-        <v>0.989</v>
+        <v>0.9424</v>
       </c>
       <c r="J200" t="n">
-        <v>18.791</v>
+        <v>17.9056</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.01</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.059</v>
+        <v>-0.0196</v>
       </c>
       <c r="J201" t="n">
-        <v>-1.121</v>
+        <v>-0.3724</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.2</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4517</v>
+        <v>0.4433</v>
       </c>
       <c r="J202" t="n">
-        <v>13.551</v>
+        <v>13.299</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.14</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3372</v>
+        <v>0.3364</v>
       </c>
       <c r="J203" t="n">
-        <v>10.116</v>
+        <v>10.092</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.1</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2567</v>
+        <v>0.26</v>
       </c>
       <c r="J204" t="n">
-        <v>7.701</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.71</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3223</v>
+        <v>-0.335</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.669</v>
+        <v>-10.05</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.66</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3696</v>
+        <v>-0.3807</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.088</v>
+        <v>-11.421</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.37</v>
       </c>
       <c r="I207" t="n">
-        <v>0.9689</v>
+        <v>0.9072</v>
       </c>
       <c r="J207" t="n">
-        <v>29.067</v>
+        <v>27.216</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.35</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9275</v>
+        <v>0.8675</v>
       </c>
       <c r="J208" t="n">
-        <v>27.825</v>
+        <v>26.025</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.17</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4973</v>
+        <v>0.486</v>
       </c>
       <c r="J209" t="n">
-        <v>14.919</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.01</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0216</v>
+        <v>0.0369</v>
       </c>
       <c r="J210" t="n">
-        <v>0.648</v>
+        <v>1.107</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6603</v>
+        <v>-0.6149</v>
       </c>
       <c r="J211" t="n">
-        <v>-19.809</v>
+        <v>-18.447</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.44</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0946</v>
+        <v>1.0467</v>
       </c>
       <c r="J212" t="n">
-        <v>39.4056</v>
+        <v>37.6812</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3529</v>
+        <v>0.3512</v>
       </c>
       <c r="J213" t="n">
-        <v>12.7044</v>
+        <v>12.6432</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.1</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3255</v>
+        <v>0.3259</v>
       </c>
       <c r="J214" t="n">
-        <v>11.718</v>
+        <v>11.7324</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.02</v>
       </c>
       <c r="I215" t="n">
-        <v>0.0766</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="J215" t="n">
-        <v>2.7576</v>
+        <v>3.1644</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.75</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.773</v>
+        <v>-0.7171</v>
       </c>
       <c r="J216" t="n">
-        <v>-27.828</v>
+        <v>-25.8156</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.05</v>
       </c>
       <c r="I217" t="n">
-        <v>0.144</v>
+        <v>0.1513</v>
       </c>
       <c r="J217" t="n">
-        <v>5.184</v>
+        <v>5.4468</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.03</v>
       </c>
       <c r="I218" t="n">
-        <v>0.096</v>
+        <v>0.103</v>
       </c>
       <c r="J218" t="n">
-        <v>3.456</v>
+        <v>3.708</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.03</v>
       </c>
       <c r="I219" t="n">
-        <v>0.096</v>
+        <v>0.103</v>
       </c>
       <c r="J219" t="n">
-        <v>3.456</v>
+        <v>3.708</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0029</v>
+        <v>0.002</v>
       </c>
       <c r="J220" t="n">
-        <v>0.1044</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2563</v>
+        <v>-0.2701</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.226800000000001</v>
+        <v>-9.723599999999999</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2.65</v>
       </c>
       <c r="I222" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J222" t="n">
-        <v>33.0084</v>
+        <v>34.8696</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.74</v>
       </c>
       <c r="I223" t="n">
-        <v>1.3509</v>
+        <v>1.343</v>
       </c>
       <c r="J223" t="n">
-        <v>24.3162</v>
+        <v>24.174</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.53</v>
       </c>
       <c r="I224" t="n">
-        <v>1.1164</v>
+        <v>1.0901</v>
       </c>
       <c r="J224" t="n">
-        <v>20.0952</v>
+        <v>19.6218</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.3</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7077</v>
+        <v>0.6937</v>
       </c>
       <c r="J225" t="n">
-        <v>12.7386</v>
+        <v>12.4866</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.02</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.0457</v>
+        <v>0.0023</v>
       </c>
       <c r="J226" t="n">
-        <v>-0.8226</v>
+        <v>0.0414</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.93</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0187</v>
+        <v>-0.048</v>
       </c>
       <c r="J227" t="n">
-        <v>-0.3366</v>
+        <v>-0.864</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.61</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.3669</v>
+        <v>-0.3869</v>
       </c>
       <c r="J228" t="n">
-        <v>-6.6042</v>
+        <v>-6.9642</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.412</v>
+        <v>-0.4298</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.416</v>
+        <v>-7.7364</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.55</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4212</v>
+        <v>-0.4386</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.5816</v>
+        <v>-7.8948</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.43</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5343</v>
+        <v>-0.5441</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.6174</v>
+        <v>-9.793799999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.36</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7689</v>
+        <v>0.7266</v>
       </c>
       <c r="J232" t="n">
-        <v>20.7603</v>
+        <v>19.6182</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.16</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3994</v>
+        <v>0.39</v>
       </c>
       <c r="J233" t="n">
-        <v>10.7838</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.85</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1763</v>
+        <v>-0.1925</v>
       </c>
       <c r="J234" t="n">
-        <v>-4.7601</v>
+        <v>-5.1975</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.66</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.362</v>
+        <v>-0.3748</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.773999999999999</v>
+        <v>-10.1196</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.47</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5365</v>
+        <v>-0.5405</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.4855</v>
+        <v>-14.5935</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.36</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9575</v>
+        <v>0.8943</v>
       </c>
       <c r="J237" t="n">
-        <v>25.8525</v>
+        <v>24.1461</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.31</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8446</v>
+        <v>0.7927</v>
       </c>
       <c r="J238" t="n">
-        <v>22.8042</v>
+        <v>21.4029</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.25</v>
       </c>
       <c r="I239" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.6667</v>
       </c>
       <c r="J239" t="n">
-        <v>18.9297</v>
+        <v>18.0009</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.93</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.292</v>
+        <v>-0.2818</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.884</v>
+        <v>-7.6086</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8312</v>
+        <v>-0.7667</v>
       </c>
       <c r="J241" t="n">
-        <v>-22.4424</v>
+        <v>-20.7009</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.26</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J242" t="n">
-        <v>33.0084</v>
+        <v>34.8696</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.96</v>
       </c>
       <c r="I243" t="n">
-        <v>1.6057</v>
+        <v>1.6104</v>
       </c>
       <c r="J243" t="n">
-        <v>28.9026</v>
+        <v>28.9872</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.29</v>
       </c>
       <c r="I244" t="n">
-        <v>0.7007</v>
+        <v>0.6846</v>
       </c>
       <c r="J244" t="n">
-        <v>12.6126</v>
+        <v>12.3228</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.19</v>
       </c>
       <c r="I245" t="n">
-        <v>0.4617</v>
+        <v>0.4719</v>
       </c>
       <c r="J245" t="n">
-        <v>8.310600000000001</v>
+        <v>8.494199999999999</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.12</v>
       </c>
       <c r="I246" t="n">
-        <v>0.2792</v>
+        <v>0.3063</v>
       </c>
       <c r="J246" t="n">
-        <v>5.0256</v>
+        <v>5.5134</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.97</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0684</v>
+        <v>0.0175</v>
       </c>
       <c r="J247" t="n">
-        <v>1.2312</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.89</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0725</v>
+        <v>-0.1015</v>
       </c>
       <c r="J248" t="n">
-        <v>-1.305</v>
+        <v>-1.827</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.51</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4593</v>
+        <v>-0.4743</v>
       </c>
       <c r="J249" t="n">
-        <v>-8.2674</v>
+        <v>-8.5374</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.43</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.535</v>
+        <v>-0.5447</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.804600000000001</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.3</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.659</v>
+        <v>-0.6589</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.862</v>
+        <v>-11.8602</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.54</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2181</v>
+        <v>1.1815</v>
       </c>
       <c r="J252" t="n">
-        <v>31.6706</v>
+        <v>30.719</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.41</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0453</v>
+        <v>0.9896</v>
       </c>
       <c r="J253" t="n">
-        <v>27.1778</v>
+        <v>25.7296</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.09</v>
       </c>
       <c r="I254" t="n">
-        <v>0.2937</v>
+        <v>0.2973</v>
       </c>
       <c r="J254" t="n">
-        <v>7.6362</v>
+        <v>7.7298</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.8</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.653</v>
+        <v>-0.6098</v>
       </c>
       <c r="J255" t="n">
-        <v>-16.978</v>
+        <v>-15.8548</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.72</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8549</v>
+        <v>-0.7876</v>
       </c>
       <c r="J256" t="n">
-        <v>-22.2274</v>
+        <v>-20.4776</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7217</v>
+        <v>0.6889</v>
       </c>
       <c r="J257" t="n">
-        <v>18.7642</v>
+        <v>17.9114</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.07</v>
       </c>
       <c r="I258" t="n">
-        <v>0.194</v>
+        <v>0.1991</v>
       </c>
       <c r="J258" t="n">
-        <v>5.044</v>
+        <v>5.1766</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.91</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1186</v>
+        <v>-0.132</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.0836</v>
+        <v>-3.432</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.91</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1186</v>
+        <v>-0.132</v>
       </c>
       <c r="J260" t="n">
-        <v>-3.0836</v>
+        <v>-3.432</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.55</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4704</v>
+        <v>-0.4771</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.2304</v>
+        <v>-12.4046</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.17</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4462</v>
+        <v>0.4283</v>
       </c>
       <c r="J262" t="n">
-        <v>11.155</v>
+        <v>10.7075</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.95</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0582</v>
+        <v>-0.0725</v>
       </c>
       <c r="J263" t="n">
-        <v>-1.455</v>
+        <v>-1.8125</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.74</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2781</v>
+        <v>-0.2949</v>
       </c>
       <c r="J264" t="n">
-        <v>-6.9525</v>
+        <v>-7.3725</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.72</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2973</v>
+        <v>-0.3136</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.4325</v>
+        <v>-7.84</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.63</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3826</v>
+        <v>-0.3958</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.565</v>
+        <v>-9.895</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.57</v>
       </c>
       <c r="I267" t="n">
-        <v>1.21</v>
+        <v>1.1814</v>
       </c>
       <c r="J267" t="n">
-        <v>30.25</v>
+        <v>29.535</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.43</v>
       </c>
       <c r="I268" t="n">
-        <v>1.0328</v>
+        <v>0.9841</v>
       </c>
       <c r="J268" t="n">
-        <v>25.82</v>
+        <v>24.6025</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.21</v>
       </c>
       <c r="I269" t="n">
-        <v>0.5693</v>
+        <v>0.5567</v>
       </c>
       <c r="J269" t="n">
-        <v>14.2325</v>
+        <v>13.9175</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.11</v>
       </c>
       <c r="I270" t="n">
-        <v>0.3109</v>
+        <v>0.3224</v>
       </c>
       <c r="J270" t="n">
-        <v>7.7725</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.1</v>
       </c>
       <c r="I271" t="n">
-        <v>0.2828</v>
+        <v>0.2965</v>
       </c>
       <c r="J271" t="n">
-        <v>7.07</v>
+        <v>7.4125</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6018/event_6018_evp_summary.xlsx
+++ b/database/event/6018/event_6018_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.8414</v>
+        <v>8.8809</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2502</v>
+        <v>1.2558</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4006</v>
+        <v>3.4399</v>
       </c>
       <c r="E2" t="n">
-        <v>8.8414</v>
+        <v>8.8809</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7649</v>
+        <v>2.7358</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0766</v>
+        <v>6.145</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3265</v>
+        <v>3.3196</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4122</v>
+        <v>3.4083</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0766</v>
+        <v>6.145</v>
       </c>
       <c r="K2" t="n">
         <v>79</v>
@@ -529,7 +529,7 @@
         <v>244</v>
       </c>
       <c r="M2" t="n">
-        <v>9.488799999999999</v>
+        <v>9.5533</v>
       </c>
       <c r="N2" t="n">
         <v>323</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.3813</v>
+        <v>7.3459</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0438</v>
+        <v>1.0388</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7359</v>
+        <v>2.7406</v>
       </c>
       <c r="E3" t="n">
-        <v>7.3813</v>
+        <v>7.3459</v>
       </c>
       <c r="F3" t="n">
-        <v>1.581</v>
+        <v>1.5798</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8003</v>
+        <v>5.7661</v>
       </c>
       <c r="H3" t="n">
-        <v>1.581</v>
+        <v>1.5798</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6217</v>
+        <v>1.622</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8003</v>
+        <v>5.7661</v>
       </c>
       <c r="K3" t="n">
         <v>79</v>
@@ -575,7 +575,7 @@
         <v>244</v>
       </c>
       <c r="M3" t="n">
-        <v>7.422</v>
+        <v>7.3881</v>
       </c>
       <c r="N3" t="n">
         <v>323</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2745</v>
+        <v>6.1747</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8873</v>
+        <v>0.8732</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2321</v>
+        <v>2.2071</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2745</v>
+        <v>6.1747</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8446</v>
+        <v>2.8651</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4299</v>
+        <v>3.3096</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4914</v>
+        <v>4.3142</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4253</v>
+        <v>2.4223</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4299</v>
+        <v>3.3096</v>
       </c>
       <c r="K4" t="n">
         <v>93</v>
@@ -621,7 +621,7 @@
         <v>175</v>
       </c>
       <c r="M4" t="n">
-        <v>5.8552</v>
+        <v>5.7319</v>
       </c>
       <c r="N4" t="n">
         <v>268</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6015</v>
+        <v>5.5001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7921</v>
+        <v>0.7778</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9257</v>
+        <v>1.8998</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6015</v>
+        <v>5.5001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0325</v>
+        <v>-0.0121</v>
       </c>
       <c r="G5" t="n">
-        <v>5.569</v>
+        <v>5.5122</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0325</v>
+        <v>-0.0121</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0333</v>
+        <v>-0.0124</v>
       </c>
       <c r="J5" t="n">
-        <v>5.569</v>
+        <v>5.5122</v>
       </c>
       <c r="K5" t="n">
         <v>79</v>
@@ -667,7 +667,7 @@
         <v>244</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6023</v>
+        <v>5.4998</v>
       </c>
       <c r="N5" t="n">
         <v>323</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7665</v>
+        <v>3.6825</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5326</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0904</v>
+        <v>1.0718</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7665</v>
+        <v>3.6825</v>
       </c>
       <c r="F6" t="n">
-        <v>3.16</v>
+        <v>3.1319</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6065</v>
+        <v>0.5506</v>
       </c>
       <c r="H6" t="n">
-        <v>5.532</v>
+        <v>5.3157</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9872</v>
+        <v>2.9846</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6065</v>
+        <v>0.5506</v>
       </c>
       <c r="K6" t="n">
         <v>93</v>
@@ -713,7 +713,7 @@
         <v>175</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5937</v>
+        <v>3.5352</v>
       </c>
       <c r="N6" t="n">
         <v>268</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5346</v>
+        <v>3.4625</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4998</v>
+        <v>0.4896</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9848</v>
+        <v>0.9715</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5346</v>
+        <v>3.4625</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2743</v>
+        <v>2.2969</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2603</v>
+        <v>1.1656</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2743</v>
+        <v>2.3136</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3329</v>
+        <v>2.3754</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2603</v>
+        <v>1.1656</v>
       </c>
       <c r="K7" t="n">
         <v>76</v>
@@ -759,7 +759,7 @@
         <v>57</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5932</v>
+        <v>3.541</v>
       </c>
       <c r="N7" t="n">
         <v>133</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>h4rn</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3593</v>
+        <v>3.2451</v>
       </c>
       <c r="C8" t="n">
-        <v>0.475</v>
+        <v>0.4589</v>
       </c>
       <c r="D8" t="n">
-        <v>0.905</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3593</v>
+        <v>3.2451</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9336</v>
+        <v>-0.3845</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4257</v>
+        <v>3.6296</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9336</v>
+        <v>-0.3845</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9336</v>
+        <v>-0.3948</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4257</v>
+        <v>3.6296</v>
       </c>
       <c r="K8" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="L8" t="n">
-        <v>106</v>
+        <v>244</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3593</v>
+        <v>3.2348</v>
       </c>
       <c r="N8" t="n">
-        <v>194</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Forester</t>
+          <t>h4rn</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2266</v>
+        <v>3.2013</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4563</v>
+        <v>0.4527</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8446</v>
+        <v>0.8526</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2266</v>
+        <v>3.2013</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7793</v>
+        <v>1.8412</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4473</v>
+        <v>1.3601</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2758</v>
+        <v>1.8412</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3089</v>
+        <v>1.8412</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4473</v>
+        <v>1.3601</v>
       </c>
       <c r="K9" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="L9" t="n">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7562</v>
+        <v>3.2013</v>
       </c>
       <c r="N9" t="n">
-        <v>268</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>Forester</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2022</v>
+        <v>3.1033</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4528</v>
+        <v>0.4388</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8335</v>
+        <v>0.8079</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2022</v>
+        <v>3.1033</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4087</v>
+        <v>2.7974</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6109</v>
+        <v>0.3059</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4087</v>
+        <v>4.0601</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4192</v>
+        <v>2.2796</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6109</v>
+        <v>0.3059</v>
       </c>
       <c r="K10" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="L10" t="n">
-        <v>244</v>
+        <v>175</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1917</v>
+        <v>2.5855</v>
       </c>
       <c r="N10" t="n">
-        <v>323</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1664</v>
+        <v>3.013</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4478</v>
+        <v>0.4261</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8172</v>
+        <v>0.7668</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1664</v>
+        <v>3.013</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9759</v>
+        <v>0.9675</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1905</v>
+        <v>2.0455</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9759</v>
+        <v>0.9675</v>
       </c>
       <c r="I11" t="n">
-        <v>0.527</v>
+        <v>0.5432</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1905</v>
+        <v>2.0455</v>
       </c>
       <c r="K11" t="n">
         <v>93</v>
@@ -943,7 +943,7 @@
         <v>175</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7175</v>
+        <v>2.5887</v>
       </c>
       <c r="N11" t="n">
         <v>268</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9147</v>
+        <v>2.8549</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4122</v>
+        <v>0.4037</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7026</v>
+        <v>0.6948</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9147</v>
+        <v>2.8549</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4146</v>
+        <v>2.376</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5001</v>
+        <v>0.4789</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5598</v>
+        <v>2.495</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6258</v>
+        <v>2.5617</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5001</v>
+        <v>0.4789</v>
       </c>
       <c r="K12" t="n">
         <v>76</v>
@@ -989,7 +989,7 @@
         <v>57</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1259</v>
+        <v>3.0406</v>
       </c>
       <c r="N12" t="n">
         <v>133</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4769</v>
+        <v>2.492</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3503</v>
+        <v>0.3524</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5033</v>
+        <v>0.5294</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4769</v>
+        <v>2.492</v>
       </c>
       <c r="F13" t="n">
-        <v>3.092</v>
+        <v>3.0726</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6151</v>
+        <v>-0.5806</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3075</v>
+        <v>5.0932</v>
       </c>
       <c r="I13" t="n">
-        <v>2.866</v>
+        <v>2.8597</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6151</v>
+        <v>-0.5806</v>
       </c>
       <c r="K13" t="n">
         <v>93</v>
@@ -1035,7 +1035,7 @@
         <v>175</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2509</v>
+        <v>2.2791</v>
       </c>
       <c r="N13" t="n">
         <v>268</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2668</v>
+        <v>2.2983</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3205</v>
+        <v>0.325</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4077</v>
+        <v>0.4412</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2668</v>
+        <v>2.2983</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4148</v>
+        <v>2.4853</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.148</v>
+        <v>-0.187</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0732</v>
+        <v>2.8883</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6595</v>
+        <v>1.6217</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.148</v>
+        <v>-0.187</v>
       </c>
       <c r="K14" t="n">
         <v>89</v>
@@ -1081,7 +1081,7 @@
         <v>49</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5115</v>
+        <v>1.4347</v>
       </c>
       <c r="N14" t="n">
         <v>138</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4516</v>
+        <v>1.4039</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2053</v>
+        <v>0.1985</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0366</v>
+        <v>0.0338</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4516</v>
+        <v>1.4039</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0335</v>
+        <v>1.9552</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5819</v>
+        <v>-0.5513</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0335</v>
+        <v>1.9552</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0981</v>
+        <v>1.0978</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5819</v>
+        <v>-0.5513</v>
       </c>
       <c r="K15" t="n">
         <v>89</v>
@@ -1127,7 +1127,7 @@
         <v>49</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5162000000000001</v>
+        <v>0.5465000000000001</v>
       </c>
       <c r="N15" t="n">
         <v>138</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DeathZz</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4024</v>
+        <v>1.346</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1983</v>
+        <v>0.1903</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0142</v>
+        <v>0.0074</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4024</v>
+        <v>1.346</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7727</v>
+        <v>0.8621</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3703</v>
+        <v>0.4839</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7727</v>
+        <v>0.8621</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8184</v>
+        <v>0.8851</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3703</v>
+        <v>0.4839</v>
       </c>
       <c r="K16" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L16" t="n">
-        <v>57</v>
+        <v>244</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4481</v>
+        <v>1.369</v>
       </c>
       <c r="N16" t="n">
-        <v>133</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>DeathZz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3819</v>
+        <v>1.2982</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1954</v>
+        <v>0.1836</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0049</v>
+        <v>-0.0144</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3819</v>
+        <v>1.2982</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8427</v>
+        <v>1.6795</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5392</v>
+        <v>-0.3813</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8427</v>
+        <v>1.6795</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8643999999999999</v>
+        <v>1.7244</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5392</v>
+        <v>-0.3813</v>
       </c>
       <c r="K17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="L17" t="n">
-        <v>244</v>
+        <v>57</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4036</v>
+        <v>1.3431</v>
       </c>
       <c r="N17" t="n">
-        <v>323</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2319</v>
+        <v>1.2116</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1742</v>
+        <v>0.1713</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0634</v>
+        <v>-0.0538</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2319</v>
+        <v>1.2116</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8295</v>
+        <v>0.8498</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4024</v>
+        <v>0.3618</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8295</v>
+        <v>0.8498</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8509</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4024</v>
+        <v>0.3618</v>
       </c>
       <c r="K18" t="n">
         <v>76</v>
@@ -1265,7 +1265,7 @@
         <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2533</v>
+        <v>1.2343</v>
       </c>
       <c r="N18" t="n">
         <v>133</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1683</v>
+        <v>1.152</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1652</v>
+        <v>0.1629</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0924</v>
+        <v>-0.081</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1683</v>
+        <v>1.152</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3385</v>
+        <v>1.2853</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1702</v>
+        <v>-0.1333</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3385</v>
+        <v>1.2853</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3385</v>
+        <v>1.2853</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1702</v>
+        <v>-0.1333</v>
       </c>
       <c r="K19" t="n">
         <v>88</v>
@@ -1311,7 +1311,7 @@
         <v>106</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1683</v>
+        <v>1.152</v>
       </c>
       <c r="N19" t="n">
         <v>194</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9144</v>
+        <v>0.8835</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1293</v>
+        <v>0.1249</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2079</v>
+        <v>-0.2033</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9144</v>
+        <v>0.8835</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5092</v>
+        <v>0.4921</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4052</v>
+        <v>0.3914</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5092</v>
+        <v>0.4921</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5223</v>
+        <v>0.5053</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4052</v>
+        <v>0.3914</v>
       </c>
       <c r="K20" t="n">
         <v>102</v>
@@ -1357,7 +1357,7 @@
         <v>69</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9275</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>171</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>forsyy</t>
+          <t>SHiPZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7752</v>
+        <v>0.6548</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1096</v>
+        <v>0.0926</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2713</v>
+        <v>-0.3075</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7752</v>
+        <v>0.6548</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4864</v>
+        <v>0.2977</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2888</v>
+        <v>0.3571</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4864</v>
+        <v>0.2977</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4989</v>
+        <v>0.2977</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2888</v>
+        <v>0.3571</v>
       </c>
       <c r="K21" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="L21" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7877000000000001</v>
+        <v>0.6548</v>
       </c>
       <c r="N21" t="n">
-        <v>171</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SHiPZ</t>
+          <t>forsyy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.72</v>
+        <v>0.6351</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1018</v>
+        <v>0.0898</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2964</v>
+        <v>-0.3165</v>
       </c>
       <c r="E22" t="n">
-        <v>0.72</v>
+        <v>0.6351</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3414</v>
+        <v>0.3951</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3786</v>
+        <v>0.2399</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3414</v>
+        <v>0.3951</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3414</v>
+        <v>0.4057</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3786</v>
+        <v>0.2399</v>
       </c>
       <c r="K22" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="L22" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="M22" t="n">
-        <v>0.72</v>
+        <v>0.6456</v>
       </c>
       <c r="N22" t="n">
-        <v>194</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.351</v>
+        <v>0.3078</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0496</v>
+        <v>0.0435</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4644</v>
+        <v>-0.4656</v>
       </c>
       <c r="E23" t="n">
-        <v>0.351</v>
+        <v>0.3078</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9333</v>
+        <v>0.8618</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5823</v>
+        <v>-0.554</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9333</v>
+        <v>0.8618</v>
       </c>
       <c r="I23" t="n">
-        <v>0.504</v>
+        <v>0.4839</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5823</v>
+        <v>-0.554</v>
       </c>
       <c r="K23" t="n">
         <v>89</v>
@@ -1495,7 +1495,7 @@
         <v>49</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.07830000000000004</v>
+        <v>-0.07010000000000005</v>
       </c>
       <c r="N23" t="n">
         <v>138</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2523</v>
+        <v>0.1989</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0357</v>
+        <v>0.0281</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5094</v>
+        <v>-0.5152</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2523</v>
+        <v>0.1989</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2523</v>
+        <v>0.1989</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2523</v>
+        <v>0.1989</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2523</v>
+        <v>0.1989</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2523</v>
+        <v>0.1989</v>
       </c>
       <c r="N24" t="n">
         <v>80</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1801</v>
+        <v>0.1752</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0255</v>
+        <v>0.0248</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5422</v>
+        <v>-0.526</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1801</v>
+        <v>0.1752</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1801</v>
+        <v>0.1752</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1801</v>
+        <v>0.1752</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1801</v>
+        <v>0.1752</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1801</v>
+        <v>0.1752</v>
       </c>
       <c r="N25" t="n">
         <v>67</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0136</v>
+        <v>-0.1074</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0019</v>
+        <v>-0.0152</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6304</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0136</v>
+        <v>-0.1074</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1702</v>
+        <v>-0.2463</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1566</v>
+        <v>0.1389</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1702</v>
+        <v>-0.2463</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0919</v>
+        <v>-0.1383</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1566</v>
+        <v>0.1389</v>
       </c>
       <c r="K26" t="n">
         <v>89</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="M26" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0005999999999999894</v>
       </c>
       <c r="N26" t="n">
         <v>138</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0794</v>
+        <v>-0.1496</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0112</v>
+        <v>-0.0212</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6603</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0794</v>
+        <v>-0.1496</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0794</v>
+        <v>-0.1496</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0794</v>
+        <v>-0.1496</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0794</v>
+        <v>-0.1496</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0794</v>
+        <v>-0.1496</v>
       </c>
       <c r="N27" t="n">
         <v>80</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0927</v>
+        <v>-0.1914</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0131</v>
+        <v>-0.0271</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6664</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0927</v>
+        <v>-0.1914</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0927</v>
+        <v>-0.1914</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0927</v>
+        <v>-0.1914</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0927</v>
+        <v>-0.1914</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0927</v>
+        <v>-0.1914</v>
       </c>
       <c r="N28" t="n">
         <v>67</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3423</v>
+        <v>-0.3145</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0484</v>
+        <v>-0.0445</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.78</v>
+        <v>-0.7491</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3423</v>
+        <v>-0.3145</v>
       </c>
       <c r="F29" t="n">
-        <v>0.201</v>
+        <v>0.1811</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5433</v>
+        <v>-0.4956</v>
       </c>
       <c r="H29" t="n">
-        <v>0.201</v>
+        <v>0.1811</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2062</v>
+        <v>0.1859</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5433</v>
+        <v>-0.4956</v>
       </c>
       <c r="K29" t="n">
         <v>102</v>
@@ -1771,7 +1771,7 @@
         <v>69</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3371</v>
+        <v>-0.3097</v>
       </c>
       <c r="N29" t="n">
         <v>171</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4501</v>
+        <v>-0.3896</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0636</v>
+        <v>-0.0551</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.7833</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4501</v>
+        <v>-0.3896</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4501</v>
+        <v>-0.3896</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4501</v>
+        <v>-0.3896</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4501</v>
+        <v>-0.3896</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4501</v>
+        <v>-0.3896</v>
       </c>
       <c r="N30" t="n">
         <v>80</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4649</v>
+        <v>-0.5295</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8358</v>
+        <v>-0.847</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4649</v>
+        <v>-0.5295</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5351</v>
+        <v>0.4705</v>
       </c>
       <c r="G31" t="n">
         <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5351</v>
+        <v>0.4705</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.4831</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>69</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4510999999999999</v>
+        <v>-0.5169</v>
       </c>
       <c r="N31" t="n">
         <v>171</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4915</v>
+        <v>-0.543</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8479</v>
+        <v>-0.8532</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4915</v>
+        <v>-0.543</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4076</v>
+        <v>-0.4296</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0839</v>
+        <v>-0.1134</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4076</v>
+        <v>-0.4296</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2201</v>
+        <v>-0.2412</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.0839</v>
+        <v>-0.1134</v>
       </c>
       <c r="K32" t="n">
         <v>89</v>
@@ -1909,7 +1909,7 @@
         <v>49</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.304</v>
+        <v>-0.3546</v>
       </c>
       <c r="N32" t="n">
         <v>138</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5123</v>
+        <v>-0.5614</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0794</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.8615</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5123</v>
+        <v>-0.5614</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5123</v>
+        <v>-0.5614</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5123</v>
+        <v>-0.5614</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5123</v>
+        <v>-0.5614</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5123</v>
+        <v>-0.5614</v>
       </c>
       <c r="N33" t="n">
         <v>67</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5851</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.081</v>
+        <v>-0.0827</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8851</v>
+        <v>-0.8723</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5851</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5851</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5851</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5851</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5851</v>
       </c>
       <c r="N34" t="n">
         <v>80</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.761</v>
+        <v>-0.7774</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1076</v>
+        <v>-0.1099</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9706</v>
+        <v>-0.9599</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.761</v>
+        <v>-0.7774</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.761</v>
+        <v>-0.7774</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.761</v>
+        <v>-0.7774</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.761</v>
+        <v>-0.7774</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.761</v>
+        <v>-0.7774</v>
       </c>
       <c r="N35" t="n">
         <v>80</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9811</v>
+        <v>-0.9458</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1387</v>
+        <v>-0.1337</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0708</v>
+        <v>-1.0366</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9811</v>
+        <v>-0.9458</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9811</v>
+        <v>-0.9458</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9811</v>
+        <v>-0.9458</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9811</v>
+        <v>-0.9458</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9811</v>
+        <v>-0.9458</v>
       </c>
       <c r="N36" t="n">
         <v>67</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0177</v>
+        <v>-1.013</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1439</v>
+        <v>-0.1432</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0875</v>
+        <v>-1.0673</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0177</v>
+        <v>-1.013</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6079</v>
+        <v>0.5339</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.6256</v>
+        <v>-1.5469</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6079</v>
+        <v>0.5339</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6079</v>
+        <v>0.5339</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.6256</v>
+        <v>-1.5469</v>
       </c>
       <c r="K37" t="n">
         <v>88</v>
@@ -2139,7 +2139,7 @@
         <v>106</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0177</v>
+        <v>-1.013</v>
       </c>
       <c r="N37" t="n">
         <v>194</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2213</v>
+        <v>-1.132</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1727</v>
+        <v>-0.1601</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1802</v>
+        <v>-1.1215</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2213</v>
+        <v>-1.132</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0305</v>
+        <v>0.023</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.2518</v>
+        <v>-1.155</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0305</v>
+        <v>0.023</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0305</v>
+        <v>0.023</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.2518</v>
+        <v>-1.155</v>
       </c>
       <c r="K38" t="n">
         <v>88</v>
@@ -2185,7 +2185,7 @@
         <v>106</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2213</v>
+        <v>-1.132</v>
       </c>
       <c r="N38" t="n">
         <v>194</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4224</v>
+        <v>-1.4133</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2011</v>
+        <v>-0.1999</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2717</v>
+        <v>-1.2496</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4224</v>
+        <v>-1.4133</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4224</v>
+        <v>-1.4133</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4224</v>
+        <v>-1.4133</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4224</v>
+        <v>-1.4133</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4224</v>
+        <v>-1.4133</v>
       </c>
       <c r="N39" t="n">
         <v>67</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6654</v>
+        <v>-1.6411</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2355</v>
+        <v>-0.2321</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3823</v>
+        <v>-1.3534</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6654</v>
+        <v>-1.6411</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.541</v>
+        <v>-1.4875</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1244</v>
+        <v>-0.1536</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.541</v>
+        <v>-1.4875</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5807</v>
+        <v>-1.5273</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1244</v>
+        <v>-0.1536</v>
       </c>
       <c r="K40" t="n">
         <v>102</v>
@@ -2277,7 +2277,7 @@
         <v>69</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7051</v>
+        <v>-1.6809</v>
       </c>
       <c r="N40" t="n">
         <v>171</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.7677</v>
+        <v>-1.7273</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.25</v>
+        <v>-0.2443</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4289</v>
+        <v>-1.3927</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.7677</v>
+        <v>-1.7273</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1455</v>
+        <v>-1.1302</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6222</v>
+        <v>-0.5971</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1455</v>
+        <v>-1.1302</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.175</v>
+        <v>-1.1604</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6222</v>
+        <v>-0.5971</v>
       </c>
       <c r="K41" t="n">
         <v>76</v>
@@ -2323,7 +2323,7 @@
         <v>57</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7972</v>
+        <v>-1.7575</v>
       </c>
       <c r="N41" t="n">
         <v>133</v>
@@ -2429,10 +2429,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.989</v>
+        <v>0.982</v>
       </c>
       <c r="J2" t="n">
-        <v>25.714</v>
+        <v>25.532</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.32</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7794</v>
+        <v>0.7575</v>
       </c>
       <c r="J3" t="n">
-        <v>20.2644</v>
+        <v>19.695</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.28</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7016</v>
+        <v>0.6761</v>
       </c>
       <c r="J4" t="n">
-        <v>18.2416</v>
+        <v>17.5786</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.22</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5785</v>
+        <v>0.549</v>
       </c>
       <c r="J5" t="n">
-        <v>15.041</v>
+        <v>14.274</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4446</v>
+        <v>0.4126</v>
       </c>
       <c r="J6" t="n">
-        <v>11.5596</v>
+        <v>10.7276</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0226</v>
+        <v>0.0172</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5876</v>
+        <v>0.4472</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.92</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1137</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.9562</v>
+        <v>-2.5636</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.85</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1898</v>
+        <v>-0.1711</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.9348</v>
+        <v>-4.4486</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.78</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2592</v>
+        <v>-0.2401</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.7392</v>
+        <v>-6.2426</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.78</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2592</v>
+        <v>-0.2401</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.7392</v>
+        <v>-6.2426</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.56</v>
       </c>
       <c r="I12" t="n">
-        <v>1.228</v>
+        <v>1.2467</v>
       </c>
       <c r="J12" t="n">
-        <v>34.384</v>
+        <v>34.9076</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9338</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>26.1464</v>
+        <v>25.8132</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.38</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8958</v>
+        <v>0.881</v>
       </c>
       <c r="J14" t="n">
-        <v>25.0824</v>
+        <v>24.668</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6006</v>
+        <v>0.5714</v>
       </c>
       <c r="J15" t="n">
-        <v>16.8168</v>
+        <v>15.9992</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6145</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.206</v>
+        <v>-16.3016</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4452</v>
+        <v>0.3928</v>
       </c>
       <c r="J17" t="n">
-        <v>12.4656</v>
+        <v>10.9984</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.11</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3116</v>
+        <v>0.2633</v>
       </c>
       <c r="J18" t="n">
-        <v>8.7248</v>
+        <v>7.3724</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.88</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1573</v>
+        <v>-0.1404</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.4044</v>
+        <v>-3.9312</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.71</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3233</v>
+        <v>-0.3066</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.0524</v>
+        <v>-8.5848</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.35</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6368</v>
+        <v>-0.6585</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.8304</v>
+        <v>-18.438</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3383</v>
+        <v>0.33</v>
       </c>
       <c r="J22" t="n">
-        <v>9.810700000000001</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.08</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1755</v>
+        <v>0.1582</v>
       </c>
       <c r="J23" t="n">
-        <v>5.0895</v>
+        <v>4.5878</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1419</v>
+        <v>-0.1233</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.1151</v>
+        <v>-3.5757</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.77</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2761</v>
+        <v>-0.257</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.0069</v>
+        <v>-7.453</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.76</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2858</v>
+        <v>-0.267</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.2882</v>
+        <v>-7.743</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.57</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7068</v>
+        <v>0.6357</v>
       </c>
       <c r="J27" t="n">
-        <v>20.4972</v>
+        <v>18.4353</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4199</v>
+        <v>0.3557</v>
       </c>
       <c r="J28" t="n">
-        <v>12.1771</v>
+        <v>10.3153</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.13</v>
       </c>
       <c r="I29" t="n">
-        <v>0.216</v>
+        <v>0.1722</v>
       </c>
       <c r="J29" t="n">
-        <v>6.264</v>
+        <v>4.9938</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1588</v>
+        <v>-0.139</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.6052</v>
+        <v>-4.031</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2545</v>
+        <v>-0.2355</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.3805</v>
+        <v>-6.8295</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0349</v>
+        <v>0.0344</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8027</v>
+        <v>0.7912</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.91</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1159</v>
+        <v>-0.1013</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.6657</v>
+        <v>-2.3299</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.84</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1939</v>
+        <v>-0.1774</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.4597</v>
+        <v>-4.0802</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2337</v>
+        <v>-0.2166</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.3751</v>
+        <v>-4.9818</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.6027</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.5746</v>
+        <v>-13.8621</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.76</v>
       </c>
       <c r="I37" t="n">
-        <v>0.859</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>19.757</v>
+        <v>18.1424</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.4</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5088</v>
+        <v>0.4423</v>
       </c>
       <c r="J38" t="n">
-        <v>11.7024</v>
+        <v>10.1729</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.28</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3833</v>
+        <v>0.3256</v>
       </c>
       <c r="J39" t="n">
-        <v>8.815899999999999</v>
+        <v>7.4888</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.16</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2414</v>
+        <v>0.1971</v>
       </c>
       <c r="J40" t="n">
-        <v>5.5522</v>
+        <v>4.5333</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.96</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0963</v>
+        <v>-0.0814</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.2149</v>
+        <v>-1.8722</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.05</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8453</v>
+        <v>1.8918</v>
       </c>
       <c r="J42" t="n">
-        <v>36.906</v>
+        <v>37.836</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>2.05</v>
       </c>
       <c r="I43" t="n">
-        <v>1.8453</v>
+        <v>1.8918</v>
       </c>
       <c r="J43" t="n">
-        <v>36.906</v>
+        <v>37.836</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.43</v>
       </c>
       <c r="I44" t="n">
-        <v>0.949</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>18.98</v>
+        <v>19.042</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.24</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5764</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>11.528</v>
+        <v>11.018</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.22</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5335</v>
+        <v>0.5056</v>
       </c>
       <c r="J46" t="n">
-        <v>10.67</v>
+        <v>10.112</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.07</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4995</v>
+        <v>0.5681</v>
       </c>
       <c r="J47" t="n">
-        <v>9.99</v>
+        <v>11.362</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.4</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.5467</v>
+        <v>-0.551</v>
       </c>
       <c r="J48" t="n">
-        <v>-10.934</v>
+        <v>-11.02</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.36</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5828</v>
+        <v>-0.5908</v>
       </c>
       <c r="J49" t="n">
-        <v>-11.656</v>
+        <v>-11.816</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.33</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6102</v>
+        <v>-0.6218</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.204</v>
+        <v>-12.436</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.2</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7308</v>
+        <v>-0.7653</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.616</v>
+        <v>-15.306</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.57</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0606</v>
+        <v>1.051</v>
       </c>
       <c r="J52" t="n">
-        <v>29.6968</v>
+        <v>29.428</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.35</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7508</v>
+        <v>0.7352</v>
       </c>
       <c r="J53" t="n">
-        <v>21.0224</v>
+        <v>20.5856</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2344</v>
+        <v>0.2039</v>
       </c>
       <c r="J54" t="n">
-        <v>6.5632</v>
+        <v>5.7092</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.93</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.291</v>
+        <v>-0.2511</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.148</v>
+        <v>-7.0308</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.91</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3471</v>
+        <v>-0.3057</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.7188</v>
+        <v>-8.5596</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.12</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3091</v>
+        <v>0.2582</v>
       </c>
       <c r="J57" t="n">
-        <v>8.6548</v>
+        <v>7.2296</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0939</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.6292</v>
+        <v>-2.2176</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1292</v>
+        <v>-0.1118</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.6176</v>
+        <v>-3.1304</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.89</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1515</v>
+        <v>-0.1329</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.242</v>
+        <v>-3.7212</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3029</v>
+        <v>-0.2849</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.481199999999999</v>
+        <v>-7.9772</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.62</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0713</v>
+        <v>1.0638</v>
       </c>
       <c r="J62" t="n">
-        <v>22.4973</v>
+        <v>22.3398</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.6</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0461</v>
+        <v>1.0381</v>
       </c>
       <c r="J63" t="n">
-        <v>21.9681</v>
+        <v>21.8001</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.56</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.9866</v>
       </c>
       <c r="J64" t="n">
-        <v>20.9055</v>
+        <v>20.7186</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.32</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6705</v>
       </c>
       <c r="J65" t="n">
-        <v>14.1939</v>
+        <v>14.0805</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.17</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4385</v>
+        <v>0.4109</v>
       </c>
       <c r="J66" t="n">
-        <v>9.208500000000001</v>
+        <v>8.6289</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.84</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1768</v>
+        <v>-0.161</v>
       </c>
       <c r="J67" t="n">
-        <v>-3.7128</v>
+        <v>-3.381</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.82</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1985</v>
+        <v>-0.1831</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.1685</v>
+        <v>-3.8451</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.65</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3596</v>
+        <v>-0.3472</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.5516</v>
+        <v>-7.2912</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3861</v>
+        <v>-0.3747</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.1081</v>
+        <v>-7.8687</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.49</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5007</v>
+        <v>-0.499</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.5147</v>
+        <v>-10.479</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>0.8</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.216</v>
+        <v>-0.201</v>
       </c>
       <c r="J72" t="n">
-        <v>-4.536</v>
+        <v>-4.221</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.72</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.2957</v>
+        <v>-0.2829</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.2097</v>
+        <v>-5.9409</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.63</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3751</v>
+        <v>-0.3638</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.8771</v>
+        <v>-7.6398</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.6</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4014</v>
+        <v>-0.3913</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.429399999999999</v>
+        <v>-8.2173</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.58</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4191</v>
+        <v>-0.41</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.8011</v>
+        <v>-8.609999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.22</v>
       </c>
       <c r="I77" t="n">
-        <v>1.7879</v>
+        <v>1.8376</v>
       </c>
       <c r="J77" t="n">
-        <v>37.5459</v>
+        <v>38.5896</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.67</v>
       </c>
       <c r="I78" t="n">
-        <v>1.1361</v>
+        <v>1.1302</v>
       </c>
       <c r="J78" t="n">
-        <v>23.8581</v>
+        <v>23.7342</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.32</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6775</v>
+        <v>0.6717</v>
       </c>
       <c r="J79" t="n">
-        <v>14.2275</v>
+        <v>14.1057</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.22</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5253</v>
+        <v>0.5225</v>
       </c>
       <c r="J80" t="n">
-        <v>11.0313</v>
+        <v>10.9725</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.76</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7489</v>
+        <v>-0.7311</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.7269</v>
+        <v>-15.3531</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.28</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5317</v>
+        <v>0.5027</v>
       </c>
       <c r="J82" t="n">
-        <v>14.8876</v>
+        <v>14.0756</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2711</v>
+        <v>0.223</v>
       </c>
       <c r="J83" t="n">
-        <v>7.5908</v>
+        <v>6.244</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.08</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2118</v>
+        <v>0.1695</v>
       </c>
       <c r="J84" t="n">
-        <v>5.9304</v>
+        <v>4.746</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1805</v>
+        <v>-0.16</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.054</v>
+        <v>-4.48</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.68</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3663</v>
+        <v>-0.353</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.2564</v>
+        <v>-9.884</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.58</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0715</v>
+        <v>1.0623</v>
       </c>
       <c r="J87" t="n">
-        <v>30.002</v>
+        <v>29.7444</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.46</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9066</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="J88" t="n">
-        <v>25.3848</v>
+        <v>24.9648</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.28</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6443</v>
+        <v>0.6317</v>
       </c>
       <c r="J89" t="n">
-        <v>18.0404</v>
+        <v>17.6876</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.97</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1672</v>
+        <v>-0.1357</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.6816</v>
+        <v>-3.7996</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.0666</v>
+        <v>-1.0768</v>
       </c>
       <c r="J91" t="n">
-        <v>-29.8648</v>
+        <v>-30.1504</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.3</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5422</v>
+        <v>0.5143</v>
       </c>
       <c r="J92" t="n">
-        <v>15.1816</v>
+        <v>14.4004</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4599</v>
+        <v>0.4096</v>
       </c>
       <c r="J93" t="n">
-        <v>12.8772</v>
+        <v>11.4688</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.22</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4468</v>
+        <v>0.3938</v>
       </c>
       <c r="J94" t="n">
-        <v>12.5104</v>
+        <v>11.0264</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0486</v>
       </c>
       <c r="J95" t="n">
-        <v>1.8508</v>
+        <v>1.3608</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4429</v>
+        <v>-0.4382</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.4012</v>
+        <v>-12.2696</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.24</v>
       </c>
       <c r="I97" t="n">
-        <v>0.604</v>
+        <v>0.5909</v>
       </c>
       <c r="J97" t="n">
-        <v>16.912</v>
+        <v>16.5452</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4505</v>
+        <v>0.4143</v>
       </c>
       <c r="J98" t="n">
-        <v>12.614</v>
+        <v>11.6004</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.11</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3571</v>
+        <v>0.3164</v>
       </c>
       <c r="J99" t="n">
-        <v>9.998799999999999</v>
+        <v>8.8592</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.96</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1777</v>
+        <v>-0.1442</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.9756</v>
+        <v>-4.0376</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.79</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6207</v>
+        <v>-0.5834</v>
       </c>
       <c r="J101" t="n">
-        <v>-17.3796</v>
+        <v>-16.3352</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8135</v>
+        <v>0.7799</v>
       </c>
       <c r="J102" t="n">
-        <v>23.5915</v>
+        <v>22.6171</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.98</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0421</v>
+        <v>-0.0321</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.2209</v>
+        <v>-0.9308999999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.97</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0575</v>
+        <v>-0.0453</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.6675</v>
+        <v>-1.3137</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.87</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1793</v>
+        <v>-0.1589</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.1997</v>
+        <v>-4.6081</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.6</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4364</v>
+        <v>-0.4299</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.6556</v>
+        <v>-12.4671</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.43</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.8857</v>
       </c>
       <c r="J107" t="n">
-        <v>26.0623</v>
+        <v>25.6853</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.19</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5229</v>
+        <v>0.5087</v>
       </c>
       <c r="J108" t="n">
-        <v>15.1641</v>
+        <v>14.7523</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.97</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1423</v>
+        <v>-0.1126</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.1267</v>
+        <v>-3.2654</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.9</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.35</v>
+        <v>-0.3074</v>
       </c>
       <c r="J110" t="n">
-        <v>-10.15</v>
+        <v>-8.9146</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.71</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7957</v>
+        <v>-0.7708</v>
       </c>
       <c r="J111" t="n">
-        <v>-23.0753</v>
+        <v>-22.3532</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.544</v>
+        <v>0.5779</v>
       </c>
       <c r="J112" t="n">
-        <v>15.232</v>
+        <v>16.1812</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1589</v>
+        <v>0.1415</v>
       </c>
       <c r="J113" t="n">
-        <v>4.4492</v>
+        <v>3.962</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.8</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2468</v>
+        <v>-0.2269</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.9104</v>
+        <v>-6.3532</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.78</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2665</v>
+        <v>-0.247</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.462</v>
+        <v>-6.916</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.67</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3696</v>
+        <v>-0.3561</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.3488</v>
+        <v>-9.970800000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.63</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6755</v>
+        <v>0.6325</v>
       </c>
       <c r="J117" t="n">
-        <v>18.914</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.29</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4039</v>
+        <v>0.3415</v>
       </c>
       <c r="J118" t="n">
-        <v>11.3092</v>
+        <v>9.561999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.27</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3815</v>
+        <v>0.3207</v>
       </c>
       <c r="J119" t="n">
-        <v>10.682</v>
+        <v>8.9796</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.87</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1952</v>
+        <v>-0.1753</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.4656</v>
+        <v>-4.9084</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2269</v>
+        <v>-0.2075</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.3532</v>
+        <v>-5.81</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.54</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9766</v>
+        <v>0.9659</v>
       </c>
       <c r="J122" t="n">
-        <v>18.5554</v>
+        <v>18.3521</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.49</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9113</v>
+        <v>0.9002</v>
       </c>
       <c r="J123" t="n">
-        <v>17.3147</v>
+        <v>17.1038</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.48</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8982</v>
+        <v>0.8871</v>
       </c>
       <c r="J124" t="n">
-        <v>17.0658</v>
+        <v>16.8549</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.32</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6815</v>
+        <v>0.6746</v>
       </c>
       <c r="J125" t="n">
-        <v>12.9485</v>
+        <v>12.8174</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.16</v>
       </c>
       <c r="I126" t="n">
-        <v>0.4253</v>
+        <v>0.3956</v>
       </c>
       <c r="J126" t="n">
-        <v>8.0807</v>
+        <v>7.5164</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0718</v>
+        <v>0.0698</v>
       </c>
       <c r="J127" t="n">
-        <v>1.3642</v>
+        <v>1.3262</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.9</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1154</v>
+        <v>-0.0998</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.1926</v>
+        <v>-1.8962</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.76</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.265</v>
+        <v>-0.2501</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.035</v>
+        <v>-4.7519</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.7</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.319</v>
+        <v>-0.3046</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.061</v>
+        <v>-5.7874</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.24</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7195</v>
+        <v>-0.7561</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.6705</v>
+        <v>-14.3659</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>2.01</v>
       </c>
       <c r="I132" t="n">
-        <v>1.5894</v>
+        <v>1.6216</v>
       </c>
       <c r="J132" t="n">
-        <v>34.9668</v>
+        <v>35.6752</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.25</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5891</v>
+        <v>0.5825</v>
       </c>
       <c r="J133" t="n">
-        <v>12.9602</v>
+        <v>12.815</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1869</v>
+        <v>0.1591</v>
       </c>
       <c r="J134" t="n">
-        <v>4.1118</v>
+        <v>3.5002</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1869</v>
+        <v>0.1591</v>
       </c>
       <c r="J135" t="n">
-        <v>4.1118</v>
+        <v>3.5002</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0466</v>
+        <v>-0.0416</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.0252</v>
+        <v>-0.9152</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.0702</v>
       </c>
       <c r="J137" t="n">
-        <v>-1.8282</v>
+        <v>-1.5444</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.88</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1549</v>
+        <v>-0.1386</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.4078</v>
+        <v>-3.0492</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1869</v>
+        <v>-0.1697</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.1118</v>
+        <v>-3.7334</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1869</v>
+        <v>-0.1697</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.1118</v>
+        <v>-3.7334</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.59</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4292</v>
+        <v>-0.4204</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.442399999999999</v>
+        <v>-9.248799999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.37</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8939</v>
+        <v>0.8762</v>
       </c>
       <c r="J142" t="n">
-        <v>26.817</v>
+        <v>26.286</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.27</v>
       </c>
       <c r="I143" t="n">
-        <v>0.6932</v>
+        <v>0.6627</v>
       </c>
       <c r="J143" t="n">
-        <v>20.796</v>
+        <v>19.881</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.25</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6196</v>
       </c>
       <c r="J144" t="n">
-        <v>19.551</v>
+        <v>18.588</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.18</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5028</v>
+        <v>0.4678</v>
       </c>
       <c r="J145" t="n">
-        <v>15.084</v>
+        <v>14.034</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4051</v>
+        <v>-0.3639</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.153</v>
+        <v>-10.917</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.11</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3051</v>
+        <v>0.2561</v>
       </c>
       <c r="J147" t="n">
-        <v>9.153</v>
+        <v>7.683</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.02</v>
       </c>
       <c r="I148" t="n">
-        <v>0.0985</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>2.955</v>
+        <v>2.187</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.84</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1999</v>
+        <v>-0.181</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.997</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.71</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3254</v>
+        <v>-0.3087</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.762</v>
+        <v>-9.260999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.65</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3803</v>
+        <v>-0.3673</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.409</v>
+        <v>-11.019</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0165</v>
+        <v>-0.0119</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.4125</v>
+        <v>-0.2975</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0917</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.2925</v>
+        <v>-1.9425</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.91</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1279</v>
+        <v>-0.1112</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.1975</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.82</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2225</v>
+        <v>-0.2028</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.5625</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2325</v>
+        <v>-0.2128</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.8125</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4724</v>
+        <v>0.4051</v>
       </c>
       <c r="J157" t="n">
-        <v>11.81</v>
+        <v>10.1275</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2712</v>
+        <v>0.2192</v>
       </c>
       <c r="J158" t="n">
-        <v>6.78</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.02</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0475</v>
+        <v>0.0331</v>
       </c>
       <c r="J159" t="n">
-        <v>1.1875</v>
+        <v>0.8275</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.97</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0512</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.63</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.96</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="J161" t="n">
-        <v>-1.9925</v>
+        <v>-1.605</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>2.03</v>
       </c>
       <c r="I162" t="n">
-        <v>1.7174</v>
+        <v>1.7676</v>
       </c>
       <c r="J162" t="n">
-        <v>34.348</v>
+        <v>35.352</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.37</v>
       </c>
       <c r="I163" t="n">
-        <v>0.8583</v>
+        <v>0.8487</v>
       </c>
       <c r="J163" t="n">
-        <v>17.166</v>
+        <v>16.974</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.37</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8583</v>
+        <v>0.8487</v>
       </c>
       <c r="J164" t="n">
-        <v>17.166</v>
+        <v>16.974</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.21</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5346</v>
+        <v>0.5069</v>
       </c>
       <c r="J165" t="n">
-        <v>10.692</v>
+        <v>10.138</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.19</v>
       </c>
       <c r="I166" t="n">
-        <v>0.4902</v>
+        <v>0.4609</v>
       </c>
       <c r="J166" t="n">
-        <v>9.804</v>
+        <v>9.218</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.04</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2044</v>
+        <v>0.1764</v>
       </c>
       <c r="J167" t="n">
-        <v>4.088</v>
+        <v>3.528</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.89</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1277</v>
+        <v>-0.1122</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.554</v>
+        <v>-2.244</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.62</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3908</v>
+        <v>-0.379</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.816</v>
+        <v>-7.58</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.62</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3908</v>
+        <v>-0.379</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.816</v>
+        <v>-7.58</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.44</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.554</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.978</v>
+        <v>-11.08</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.17</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3822</v>
+        <v>0.3267</v>
       </c>
       <c r="J172" t="n">
-        <v>13.7592</v>
+        <v>11.7612</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3466</v>
+        <v>0.2929</v>
       </c>
       <c r="J173" t="n">
-        <v>12.4776</v>
+        <v>10.5444</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.08</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2127</v>
+        <v>0.1703</v>
       </c>
       <c r="J174" t="n">
-        <v>7.6572</v>
+        <v>6.1308</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.99</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0251</v>
+        <v>-0.0181</v>
       </c>
       <c r="J175" t="n">
-        <v>-0.9036</v>
+        <v>-0.6516</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.437</v>
+        <v>-0.4308</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.732</v>
+        <v>-15.5088</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.32</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8418</v>
+        <v>0.8194</v>
       </c>
       <c r="J177" t="n">
-        <v>30.3048</v>
+        <v>29.4984</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5097</v>
+        <v>0.4681</v>
       </c>
       <c r="J178" t="n">
-        <v>18.3492</v>
+        <v>16.8516</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.01</v>
       </c>
       <c r="I179" t="n">
-        <v>0.056</v>
+        <v>0.0416</v>
       </c>
       <c r="J179" t="n">
-        <v>2.016</v>
+        <v>1.4976</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.85</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4743</v>
+        <v>-0.4316</v>
       </c>
       <c r="J180" t="n">
-        <v>-17.0748</v>
+        <v>-15.5376</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.78</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.602</v>
       </c>
       <c r="J181" t="n">
-        <v>-22.9896</v>
+        <v>-21.672</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.27</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5395</v>
+        <v>0.4798</v>
       </c>
       <c r="J182" t="n">
-        <v>14.5665</v>
+        <v>12.9546</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.02</v>
       </c>
       <c r="I183" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="J183" t="n">
-        <v>1.89</v>
+        <v>1.377</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.99</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0278</v>
+        <v>-0.0197</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.7506</v>
+        <v>-0.5319</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.97</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0611</v>
+        <v>-0.0478</v>
       </c>
       <c r="J185" t="n">
-        <v>-1.6497</v>
+        <v>-1.2906</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.95</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.0892</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J186" t="n">
-        <v>-2.4084</v>
+        <v>-1.9683</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.21</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5828</v>
+        <v>0.5447</v>
       </c>
       <c r="J187" t="n">
-        <v>15.7356</v>
+        <v>14.7069</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.422</v>
+        <v>0.3825</v>
       </c>
       <c r="J188" t="n">
-        <v>11.394</v>
+        <v>10.3275</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.08</v>
       </c>
       <c r="I189" t="n">
-        <v>0.272</v>
+        <v>0.2375</v>
       </c>
       <c r="J189" t="n">
-        <v>7.344</v>
+        <v>6.4125</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.05</v>
       </c>
       <c r="I190" t="n">
-        <v>0.186</v>
+        <v>0.1573</v>
       </c>
       <c r="J190" t="n">
-        <v>5.022</v>
+        <v>4.2471</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.03</v>
       </c>
       <c r="I191" t="n">
-        <v>0.1212</v>
+        <v>0.0988</v>
       </c>
       <c r="J191" t="n">
-        <v>3.2724</v>
+        <v>2.6676</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.07</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3062</v>
+        <v>0.2806</v>
       </c>
       <c r="J192" t="n">
-        <v>5.8178</v>
+        <v>5.3314</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.84</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1738</v>
+        <v>-0.1576</v>
       </c>
       <c r="J193" t="n">
-        <v>-3.3022</v>
+        <v>-2.9944</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.51</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4813</v>
+        <v>-0.4774</v>
       </c>
       <c r="J194" t="n">
-        <v>-9.1447</v>
+        <v>-9.070600000000001</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.49</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4989</v>
+        <v>-0.4969</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.479100000000001</v>
+        <v>-9.4411</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.44</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5427</v>
+        <v>-0.5462</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.3113</v>
+        <v>-10.3778</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.99</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6579</v>
+        <v>1.7017</v>
       </c>
       <c r="J197" t="n">
-        <v>31.5001</v>
+        <v>32.3323</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.6</v>
       </c>
       <c r="I198" t="n">
-        <v>1.1888</v>
+        <v>1.2073</v>
       </c>
       <c r="J198" t="n">
-        <v>22.5872</v>
+        <v>22.9387</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.45</v>
       </c>
       <c r="I199" t="n">
-        <v>0.992</v>
+        <v>0.9987</v>
       </c>
       <c r="J199" t="n">
-        <v>18.848</v>
+        <v>18.9753</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.42</v>
       </c>
       <c r="I200" t="n">
-        <v>0.9424</v>
+        <v>0.9427</v>
       </c>
       <c r="J200" t="n">
-        <v>17.9056</v>
+        <v>17.9113</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.01</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.0196</v>
+        <v>-0.0347</v>
       </c>
       <c r="J201" t="n">
-        <v>-0.3724</v>
+        <v>-0.6593</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.2</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4433</v>
+        <v>0.3859</v>
       </c>
       <c r="J202" t="n">
-        <v>13.299</v>
+        <v>11.577</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.14</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3364</v>
+        <v>0.2833</v>
       </c>
       <c r="J203" t="n">
-        <v>10.092</v>
+        <v>8.499000000000001</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.1</v>
       </c>
       <c r="I204" t="n">
-        <v>0.26</v>
+        <v>0.2124</v>
       </c>
       <c r="J204" t="n">
-        <v>7.8</v>
+        <v>6.372</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.71</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.335</v>
+        <v>-0.319</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.05</v>
+        <v>-9.57</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.66</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3807</v>
+        <v>-0.3683</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.421</v>
+        <v>-11.049</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.37</v>
       </c>
       <c r="I207" t="n">
-        <v>0.9072</v>
+        <v>0.8899</v>
       </c>
       <c r="J207" t="n">
-        <v>27.216</v>
+        <v>26.697</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.35</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8675</v>
+        <v>0.8466</v>
       </c>
       <c r="J208" t="n">
-        <v>26.025</v>
+        <v>25.398</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.17</v>
       </c>
       <c r="I209" t="n">
-        <v>0.486</v>
+        <v>0.4482</v>
       </c>
       <c r="J209" t="n">
-        <v>14.58</v>
+        <v>13.446</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.01</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0369</v>
+        <v>0.0266</v>
       </c>
       <c r="J210" t="n">
-        <v>1.107</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6149</v>
+        <v>-0.579</v>
       </c>
       <c r="J211" t="n">
-        <v>-18.447</v>
+        <v>-17.37</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.44</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0467</v>
+        <v>1.0527</v>
       </c>
       <c r="J212" t="n">
-        <v>37.6812</v>
+        <v>37.8972</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3512</v>
+        <v>0.3124</v>
       </c>
       <c r="J213" t="n">
-        <v>12.6432</v>
+        <v>11.2464</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.1</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3259</v>
+        <v>0.2879</v>
       </c>
       <c r="J214" t="n">
-        <v>11.7324</v>
+        <v>10.3644</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.02</v>
       </c>
       <c r="I215" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="J215" t="n">
-        <v>3.1644</v>
+        <v>2.5056</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.75</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7171</v>
+        <v>-0.6867</v>
       </c>
       <c r="J216" t="n">
-        <v>-25.8156</v>
+        <v>-24.7212</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.05</v>
       </c>
       <c r="I217" t="n">
-        <v>0.1513</v>
+        <v>0.1163</v>
       </c>
       <c r="J217" t="n">
-        <v>5.4468</v>
+        <v>4.1868</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.03</v>
       </c>
       <c r="I218" t="n">
-        <v>0.103</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="J218" t="n">
-        <v>3.708</v>
+        <v>2.7288</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.03</v>
       </c>
       <c r="I219" t="n">
-        <v>0.103</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>3.708</v>
+        <v>2.7288</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1</v>
       </c>
       <c r="I220" t="n">
-        <v>0.002</v>
+        <v>0.0009</v>
       </c>
       <c r="J220" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0324</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.78</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2701</v>
+        <v>-0.2507</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.723599999999999</v>
+        <v>-9.0252</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>2.65</v>
       </c>
       <c r="I222" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J222" t="n">
-        <v>34.8696</v>
+        <v>35.6724</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.74</v>
       </c>
       <c r="I223" t="n">
-        <v>1.343</v>
+        <v>1.3701</v>
       </c>
       <c r="J223" t="n">
-        <v>24.174</v>
+        <v>24.6618</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.53</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0901</v>
+        <v>1.112</v>
       </c>
       <c r="J224" t="n">
-        <v>19.6218</v>
+        <v>20.016</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.3</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6937</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J225" t="n">
-        <v>12.4866</v>
+        <v>12.1662</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.02</v>
       </c>
       <c r="I226" t="n">
-        <v>0.0023</v>
+        <v>-0.0233</v>
       </c>
       <c r="J226" t="n">
-        <v>0.0414</v>
+        <v>-0.4194</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.93</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.048</v>
+        <v>-0.0254</v>
       </c>
       <c r="J227" t="n">
-        <v>-0.864</v>
+        <v>-0.4572</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.61</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.3869</v>
+        <v>-0.378</v>
       </c>
       <c r="J228" t="n">
-        <v>-6.9642</v>
+        <v>-6.804</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.4298</v>
+        <v>-0.4225</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.7364</v>
+        <v>-7.605</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.55</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4386</v>
+        <v>-0.4317</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.8948</v>
+        <v>-7.7706</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.43</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5441</v>
+        <v>-0.5474</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.793799999999999</v>
+        <v>-9.853199999999999</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.36</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7266</v>
+        <v>0.6778</v>
       </c>
       <c r="J232" t="n">
-        <v>19.6182</v>
+        <v>18.3006</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.16</v>
       </c>
       <c r="I233" t="n">
-        <v>0.39</v>
+        <v>0.3358</v>
       </c>
       <c r="J233" t="n">
-        <v>10.53</v>
+        <v>9.066599999999999</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.85</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1925</v>
+        <v>-0.1729</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.1975</v>
+        <v>-4.6683</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.66</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3748</v>
+        <v>-0.3614</v>
       </c>
       <c r="J235" t="n">
-        <v>-10.1196</v>
+        <v>-9.7578</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.47</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5405</v>
+        <v>-0.5467</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.5935</v>
+        <v>-14.7609</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.36</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8943</v>
+        <v>0.8756</v>
       </c>
       <c r="J237" t="n">
-        <v>24.1461</v>
+        <v>23.6412</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.31</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7927</v>
+        <v>0.7657</v>
       </c>
       <c r="J238" t="n">
-        <v>21.4029</v>
+        <v>20.6739</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.25</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6667</v>
+        <v>0.6323</v>
       </c>
       <c r="J239" t="n">
-        <v>18.0009</v>
+        <v>17.0721</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.93</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2818</v>
+        <v>-0.2415</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.6086</v>
+        <v>-6.5205</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.73</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7667</v>
+        <v>-0.7411</v>
       </c>
       <c r="J241" t="n">
-        <v>-20.7009</v>
+        <v>-20.0097</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>2.26</v>
       </c>
       <c r="I242" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J242" t="n">
-        <v>34.8696</v>
+        <v>35.6724</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.96</v>
       </c>
       <c r="I243" t="n">
-        <v>1.6104</v>
+        <v>1.6504</v>
       </c>
       <c r="J243" t="n">
-        <v>28.9872</v>
+        <v>29.7072</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.29</v>
       </c>
       <c r="I244" t="n">
-        <v>0.6846</v>
+        <v>0.6659</v>
       </c>
       <c r="J244" t="n">
-        <v>12.3228</v>
+        <v>11.9862</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.19</v>
       </c>
       <c r="I245" t="n">
-        <v>0.4719</v>
+        <v>0.4413</v>
       </c>
       <c r="J245" t="n">
-        <v>8.494199999999999</v>
+        <v>7.9434</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>1.12</v>
       </c>
       <c r="I246" t="n">
-        <v>0.3063</v>
+        <v>0.2712</v>
       </c>
       <c r="J246" t="n">
-        <v>5.5134</v>
+        <v>4.8816</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.97</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0175</v>
+        <v>0.0507</v>
       </c>
       <c r="J247" t="n">
-        <v>0.315</v>
+        <v>0.9126</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.89</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1015</v>
+        <v>-0.0806</v>
       </c>
       <c r="J248" t="n">
-        <v>-1.827</v>
+        <v>-1.4508</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.51</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4743</v>
+        <v>-0.4699</v>
       </c>
       <c r="J249" t="n">
-        <v>-8.5374</v>
+        <v>-8.4582</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.43</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5447</v>
+        <v>-0.5481</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.804600000000001</v>
+        <v>-9.8658</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.3</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6589</v>
+        <v>-0.681</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.8602</v>
+        <v>-12.258</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.54</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1815</v>
+        <v>1.1976</v>
       </c>
       <c r="J252" t="n">
-        <v>30.719</v>
+        <v>31.1376</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.41</v>
       </c>
       <c r="I253" t="n">
-        <v>0.9896</v>
+        <v>0.9847</v>
       </c>
       <c r="J253" t="n">
-        <v>25.7296</v>
+        <v>25.6022</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.09</v>
       </c>
       <c r="I254" t="n">
-        <v>0.2973</v>
+        <v>0.262</v>
       </c>
       <c r="J254" t="n">
-        <v>7.7298</v>
+        <v>6.812</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.8</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.6098</v>
+        <v>-0.573</v>
       </c>
       <c r="J255" t="n">
-        <v>-15.8548</v>
+        <v>-14.898</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.72</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7876</v>
+        <v>-0.7637</v>
       </c>
       <c r="J256" t="n">
-        <v>-20.4776</v>
+        <v>-19.8562</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6889</v>
+        <v>0.6341</v>
       </c>
       <c r="J257" t="n">
-        <v>17.9114</v>
+        <v>16.4866</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.07</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1991</v>
+        <v>0.1577</v>
       </c>
       <c r="J258" t="n">
-        <v>5.1766</v>
+        <v>4.1002</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.91</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.132</v>
+        <v>-0.1135</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.432</v>
+        <v>-2.951</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.91</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.132</v>
+        <v>-0.1135</v>
       </c>
       <c r="J260" t="n">
-        <v>-3.432</v>
+        <v>-2.951</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.55</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4771</v>
+        <v>-0.4752</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.4046</v>
+        <v>-12.3552</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.17</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4283</v>
+        <v>0.3764</v>
       </c>
       <c r="J262" t="n">
-        <v>10.7075</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.95</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.0725</v>
+        <v>-0.0605</v>
       </c>
       <c r="J263" t="n">
-        <v>-1.8125</v>
+        <v>-1.5125</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.74</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2949</v>
+        <v>-0.277</v>
       </c>
       <c r="J264" t="n">
-        <v>-7.3725</v>
+        <v>-6.925</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.72</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3136</v>
+        <v>-0.2965</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.84</v>
+        <v>-7.4125</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.63</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3958</v>
+        <v>-0.384</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.895</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.57</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1814</v>
+        <v>1.1956</v>
       </c>
       <c r="J267" t="n">
-        <v>29.535</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.43</v>
       </c>
       <c r="I268" t="n">
-        <v>0.9841</v>
+        <v>0.9804</v>
       </c>
       <c r="J268" t="n">
-        <v>24.6025</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.21</v>
       </c>
       <c r="I269" t="n">
-        <v>0.5567</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="J269" t="n">
-        <v>13.9175</v>
+        <v>13.1675</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.11</v>
       </c>
       <c r="I270" t="n">
-        <v>0.3224</v>
+        <v>0.2905</v>
       </c>
       <c r="J270" t="n">
-        <v>8.06</v>
+        <v>7.2625</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.1</v>
       </c>
       <c r="I271" t="n">
-        <v>0.2965</v>
+        <v>0.265</v>
       </c>
       <c r="J271" t="n">
-        <v>7.4125</v>
+        <v>6.625</v>
       </c>
     </row>
   </sheetData>
